--- a/document/タスク一覧表示機能テスト.xlsx
+++ b/document/タスク一覧表示機能テスト.xlsx
@@ -3,21 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA8A1E19-3AF1-41BD-8273-875042576BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176BD691-D9D0-4AF6-8914-2A2EC7EF770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="17910" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId4"/>
+    <sheet name="テスト仕様書兼報告書" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="範囲１" localSheetId="0">#REF!</definedName>
+    <definedName name="範囲１" localSheetId="4">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="120">
   <si>
     <t>（１）概要</t>
     <rPh sb="3" eb="5">
@@ -615,6 +617,220 @@
       <t>ケン</t>
     </rPh>
     <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移すること</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>メニュー画面を表示できるか確認する</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>一覧表示画面で「メニューへ」ボタンを押下する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>機能観点</t>
+    <rPh sb="0" eb="4">
+      <t>キノウカンテン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>「登録されているタスクはありません。」
+と表示されること</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>タスク0件時の表示を確認する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>タスク情報が0件の状態で一覧表示画面を表示する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>期限欄が空文字で表示されること</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>任意項目の期限が仕様通り表示されるか確認する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>期限がNULLのタスクを含む状態で一覧表示画面を表示する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>画面観点</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>担当者IDとログイン中ユーザIDが一致しない
+タスクは「-」が表示されること</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>他担当者のタスクが選択不可か確認する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>一覧表示画面をする</t>
+    <rPh sb="0" eb="6">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>担当者IDとログイン中ユーザIDが一致するタスクにラジオボタンが表示されること</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>ログインユーザ本人のタスクが選択可能か確認する</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>一覧表示画面を表示する</t>
+    <rPh sb="0" eb="6">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>タスク名・カテゴリ情報・期限・担当者情報
+・ステータス情報・メモが表示されること</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>タスク情報が表示されるか確認する</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>一覧表示画面を表示する</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>タスク一覧表示画面が表示されること</t>
+    <rPh sb="3" eb="9">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>初期表示が仕様どうりか確認する</t>
+    <rPh sb="0" eb="4">
+      <t>ショキヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>メニュー画面で「タスク一覧」を選択する</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>画面観点</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンカンテン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>検証内容</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>テスト手順</t>
+    <rPh sb="3" eb="5">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>タスク管理システム一覧表示機能</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="9" eb="15">
+      <t>イチランヒョウジキノウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>結合テスト仕様書兼報告書</t>
+    <rPh sb="0" eb="2">
+      <t>ケツゴウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
       <t>ホウコクショ</t>
     </rPh>
     <phoneticPr fontId="16"/>
@@ -1583,7 +1799,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1636,6 +1852,246 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="68" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="69" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1666,377 +2122,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="9" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="68" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="69" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2249,12 +2480,19 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="別紙"/>
+      <sheetName val="サンプル"/>
+      <sheetName val="テストケースに記載する要素"/>
+      <sheetName val="テスト用語"/>
+      <sheetName val="テスト観点一覧"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2526,1213 +2764,1366 @@
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="98" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="99" customWidth="1"/>
-    <col min="3" max="6" width="7.125" style="98" customWidth="1"/>
-    <col min="7" max="7" width="7.125" style="99" customWidth="1"/>
-    <col min="8" max="13" width="7.125" style="98" customWidth="1"/>
-    <col min="14" max="19" width="10.625" style="98" customWidth="1"/>
-    <col min="20" max="16384" width="7" style="98"/>
+    <col min="1" max="1" width="11.875" style="44" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="45" customWidth="1"/>
+    <col min="3" max="6" width="7.125" style="44" customWidth="1"/>
+    <col min="7" max="7" width="7.125" style="45" customWidth="1"/>
+    <col min="8" max="13" width="7.125" style="44" customWidth="1"/>
+    <col min="14" max="19" width="10.625" style="44" customWidth="1"/>
+    <col min="20" max="16384" width="7" style="44"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="150" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="147" t="s">
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="144" t="s">
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="O1" s="147" t="s">
+      <c r="O1" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="144" t="s">
+      <c r="P1" s="79"/>
+      <c r="Q1" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="R1" s="147" t="s">
+      <c r="R1" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="145"/>
+      <c r="S1" s="79"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="151"/>
-      <c r="B2" s="151"/>
-      <c r="C2" s="150" t="s">
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="149"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="147" t="s">
+      <c r="D2" s="75"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="144" t="s">
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="143">
+      <c r="O2" s="94">
         <v>46199</v>
       </c>
-      <c r="P2" s="142"/>
-      <c r="Q2" s="141" t="s">
+      <c r="P2" s="95"/>
+      <c r="Q2" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="140">
+      <c r="R2" s="96">
         <v>44771</v>
       </c>
-      <c r="S2" s="139"/>
+      <c r="S2" s="97"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="137"/>
-      <c r="O3" s="137"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="137"/>
-      <c r="R3" s="137"/>
-      <c r="S3" s="137"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="134" t="s">
+      <c r="A4" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="133" t="s">
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="133" t="s">
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="135"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="134" t="s">
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="R4" s="133" t="s">
+      <c r="R4" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="S4" s="132"/>
+      <c r="S4" s="62"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
-      <c r="A5" s="120">
+      <c r="A5" s="49">
         <v>1</v>
       </c>
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="131" t="s">
+      <c r="C5" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="131" t="s">
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="128" t="s">
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="O5" s="127"/>
-      <c r="P5" s="126"/>
-      <c r="Q5" s="113">
+      <c r="O5" s="89"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="48">
         <v>46198</v>
       </c>
-      <c r="R5" s="125" t="s">
+      <c r="R5" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="S5" s="124"/>
+      <c r="S5" s="84"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
-      <c r="A6" s="101">
+      <c r="A6" s="46">
         <v>2</v>
       </c>
-      <c r="B6" s="120" t="s">
+      <c r="B6" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="123" t="s">
+      <c r="C6" s="69"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="122"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="113">
+      <c r="O6" s="92"/>
+      <c r="P6" s="93"/>
+      <c r="Q6" s="48">
         <v>46198</v>
       </c>
-      <c r="R6" s="100" t="s">
+      <c r="R6" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="S6" s="100"/>
+      <c r="S6" s="72"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
-      <c r="A7" s="101">
+      <c r="A7" s="46">
         <v>3</v>
       </c>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="117"/>
-      <c r="N7" s="104" t="s">
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="O7" s="103"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="113">
+      <c r="O7" s="86"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="48">
         <v>46198</v>
       </c>
-      <c r="R7" s="100" t="s">
+      <c r="R7" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="S7" s="100"/>
+      <c r="S7" s="72"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
-      <c r="A8" s="101">
+      <c r="A8" s="46">
         <v>4</v>
       </c>
-      <c r="B8" s="120" t="s">
+      <c r="B8" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="117"/>
-      <c r="N8" s="104" t="s">
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="103"/>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="113">
+      <c r="O8" s="86"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="48">
         <v>46198</v>
       </c>
-      <c r="R8" s="100" t="s">
+      <c r="R8" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="S8" s="100"/>
+      <c r="S8" s="72"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
-      <c r="A9" s="101">
+      <c r="A9" s="46">
         <v>5</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="119"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="116"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="115"/>
-      <c r="L9" s="115"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="104" t="s">
+      <c r="C9" s="69"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="O9" s="103"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="113">
+      <c r="O9" s="86"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="48">
         <v>46198</v>
       </c>
-      <c r="R9" s="100" t="s">
+      <c r="R9" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="S9" s="100"/>
+      <c r="S9" s="72"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
-      <c r="A10" s="101"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="100"/>
-      <c r="S10" s="100"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="86"/>
+      <c r="P10" s="87"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
-      <c r="A11" s="101"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="104"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="100"/>
-      <c r="S11" s="100"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="86"/>
+      <c r="P11" s="87"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
-      <c r="A12" s="101"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="105"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="102"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="100"/>
-      <c r="S12" s="100"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
-      <c r="A13" s="101"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="103"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="100"/>
-      <c r="S13" s="100"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
-      <c r="A14" s="101"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="104"/>
-      <c r="O14" s="103"/>
-      <c r="P14" s="102"/>
-      <c r="Q14" s="101"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="100"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
-      <c r="A15" s="101"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="104"/>
-      <c r="O15" s="103"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="101"/>
-      <c r="R15" s="100"/>
-      <c r="S15" s="100"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
-      <c r="A16" s="101"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="104"/>
-      <c r="O16" s="103"/>
-      <c r="P16" s="102"/>
-      <c r="Q16" s="101"/>
-      <c r="R16" s="100"/>
-      <c r="S16" s="100"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="86"/>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
-      <c r="A17" s="101"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="105"/>
-      <c r="N17" s="104"/>
-      <c r="O17" s="103"/>
-      <c r="P17" s="102"/>
-      <c r="Q17" s="101"/>
-      <c r="R17" s="100"/>
-      <c r="S17" s="100"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
-      <c r="A18" s="101"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="108"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="105"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="102"/>
-      <c r="Q18" s="101"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="100"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="86"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="104"/>
-      <c r="O19" s="103"/>
-      <c r="P19" s="102"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
-      <c r="A20" s="101"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="108"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="103"/>
-      <c r="P20" s="102"/>
-      <c r="Q20" s="101"/>
-      <c r="R20" s="100"/>
-      <c r="S20" s="100"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="86"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
-      <c r="A21" s="101"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="105"/>
-      <c r="N21" s="104"/>
-      <c r="O21" s="103"/>
-      <c r="P21" s="102"/>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="100"/>
-      <c r="S21" s="100"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="86"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="108"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="104"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="102"/>
-      <c r="Q22" s="101"/>
-      <c r="R22" s="100"/>
-      <c r="S22" s="100"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="87"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="108"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="103"/>
-      <c r="P23" s="102"/>
-      <c r="Q23" s="101"/>
-      <c r="R23" s="100"/>
-      <c r="S23" s="100"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="86"/>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
-      <c r="A24" s="101"/>
-      <c r="B24" s="101"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="108"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="108"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="103"/>
-      <c r="P24" s="102"/>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="100"/>
-      <c r="S24" s="100"/>
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
-      <c r="A25" s="101"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="102"/>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="100"/>
-      <c r="S25" s="100"/>
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
-      <c r="A26" s="101"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="108"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="108"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="105"/>
-      <c r="N26" s="104"/>
-      <c r="O26" s="103"/>
-      <c r="P26" s="102"/>
-      <c r="Q26" s="101"/>
-      <c r="R26" s="100"/>
-      <c r="S26" s="100"/>
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="87"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
-      <c r="A27" s="101"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="108"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="102"/>
-      <c r="Q27" s="101"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="100"/>
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="86"/>
+      <c r="P27" s="87"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
-      <c r="A28" s="101"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="107"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="104"/>
-      <c r="O28" s="103"/>
-      <c r="P28" s="102"/>
-      <c r="Q28" s="101"/>
-      <c r="R28" s="100"/>
-      <c r="S28" s="100"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="87"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
-      <c r="A29" s="101"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="108"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="107"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="105"/>
-      <c r="N29" s="104"/>
-      <c r="O29" s="103"/>
-      <c r="P29" s="102"/>
-      <c r="Q29" s="101"/>
-      <c r="R29" s="100"/>
-      <c r="S29" s="100"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="87"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
-      <c r="A30" s="101"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="107"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="105"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="103"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="101"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="100"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="87"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
-      <c r="A31" s="101"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="107"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="101"/>
-      <c r="R31" s="100"/>
-      <c r="S31" s="100"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="86"/>
+      <c r="P31" s="87"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
-      <c r="A32" s="101"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="108"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="106"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="103"/>
-      <c r="P32" s="102"/>
-      <c r="Q32" s="101"/>
-      <c r="R32" s="100"/>
-      <c r="S32" s="100"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="86"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
-      <c r="A33" s="101"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="108"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="105"/>
-      <c r="N33" s="104"/>
-      <c r="O33" s="103"/>
-      <c r="P33" s="102"/>
-      <c r="Q33" s="101"/>
-      <c r="R33" s="100"/>
-      <c r="S33" s="100"/>
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="87"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
-      <c r="A34" s="101"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="108"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="107"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="105"/>
-      <c r="N34" s="104"/>
-      <c r="O34" s="103"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="101"/>
-      <c r="R34" s="100"/>
-      <c r="S34" s="100"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="85"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="87"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
-      <c r="A35" s="101"/>
-      <c r="B35" s="101"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="107"/>
-      <c r="I35" s="106"/>
-      <c r="J35" s="106"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="105"/>
-      <c r="N35" s="104"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="102"/>
-      <c r="Q35" s="101"/>
-      <c r="R35" s="100"/>
-      <c r="S35" s="100"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="72"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
-      <c r="A36" s="101"/>
-      <c r="B36" s="101"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="105"/>
-      <c r="N36" s="104"/>
-      <c r="O36" s="103"/>
-      <c r="P36" s="102"/>
-      <c r="Q36" s="101"/>
-      <c r="R36" s="100"/>
-      <c r="S36" s="100"/>
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="87"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
-      <c r="A37" s="101"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="107"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="104"/>
-      <c r="O37" s="103"/>
-      <c r="P37" s="102"/>
-      <c r="Q37" s="101"/>
-      <c r="R37" s="100"/>
-      <c r="S37" s="100"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="86"/>
+      <c r="P37" s="87"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="72"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
-      <c r="A38" s="101"/>
-      <c r="B38" s="101"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="107"/>
-      <c r="I38" s="106"/>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="105"/>
-      <c r="N38" s="104"/>
-      <c r="O38" s="103"/>
-      <c r="P38" s="102"/>
-      <c r="Q38" s="101"/>
-      <c r="R38" s="100"/>
-      <c r="S38" s="100"/>
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="86"/>
+      <c r="P38" s="87"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="72"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
-      <c r="A39" s="101"/>
-      <c r="B39" s="101"/>
-      <c r="C39" s="108"/>
-      <c r="D39" s="108"/>
-      <c r="E39" s="108"/>
-      <c r="F39" s="108"/>
-      <c r="G39" s="108"/>
-      <c r="H39" s="107"/>
-      <c r="I39" s="106"/>
-      <c r="J39" s="106"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="105"/>
-      <c r="N39" s="104"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="102"/>
-      <c r="Q39" s="101"/>
-      <c r="R39" s="100"/>
-      <c r="S39" s="100"/>
+      <c r="A39" s="46"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="86"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="72"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
-      <c r="A40" s="101"/>
-      <c r="B40" s="101"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
-      <c r="E40" s="108"/>
-      <c r="F40" s="108"/>
-      <c r="G40" s="108"/>
-      <c r="H40" s="107"/>
-      <c r="I40" s="106"/>
-      <c r="J40" s="106"/>
-      <c r="K40" s="106"/>
-      <c r="L40" s="106"/>
-      <c r="M40" s="105"/>
-      <c r="N40" s="104"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="102"/>
-      <c r="Q40" s="101"/>
-      <c r="R40" s="100"/>
-      <c r="S40" s="100"/>
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="87"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="72"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
-      <c r="A41" s="101"/>
-      <c r="B41" s="101"/>
-      <c r="C41" s="108"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="108"/>
-      <c r="F41" s="108"/>
-      <c r="G41" s="108"/>
-      <c r="H41" s="107"/>
-      <c r="I41" s="106"/>
-      <c r="J41" s="106"/>
-      <c r="K41" s="106"/>
-      <c r="L41" s="106"/>
-      <c r="M41" s="105"/>
-      <c r="N41" s="104"/>
-      <c r="O41" s="103"/>
-      <c r="P41" s="102"/>
-      <c r="Q41" s="101"/>
-      <c r="R41" s="100"/>
-      <c r="S41" s="100"/>
+      <c r="A41" s="46"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="72"/>
+      <c r="S41" s="72"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
-      <c r="A42" s="101"/>
-      <c r="B42" s="101"/>
-      <c r="C42" s="108"/>
-      <c r="D42" s="108"/>
-      <c r="E42" s="108"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="107"/>
-      <c r="I42" s="106"/>
-      <c r="J42" s="106"/>
-      <c r="K42" s="106"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="105"/>
-      <c r="N42" s="104"/>
-      <c r="O42" s="103"/>
-      <c r="P42" s="102"/>
-      <c r="Q42" s="101"/>
-      <c r="R42" s="100"/>
-      <c r="S42" s="100"/>
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="58"/>
+      <c r="N42" s="85"/>
+      <c r="O42" s="86"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="72"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
-      <c r="A43" s="101"/>
-      <c r="B43" s="101"/>
-      <c r="C43" s="108"/>
-      <c r="D43" s="108"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
-      <c r="H43" s="107"/>
-      <c r="I43" s="106"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="106"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="105"/>
-      <c r="N43" s="104"/>
-      <c r="O43" s="103"/>
-      <c r="P43" s="102"/>
-      <c r="Q43" s="101"/>
-      <c r="R43" s="100"/>
-      <c r="S43" s="100"/>
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="85"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="87"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="72"/>
+      <c r="S43" s="72"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
-      <c r="A44" s="101"/>
-      <c r="B44" s="101"/>
-      <c r="C44" s="108"/>
-      <c r="D44" s="108"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="107"/>
-      <c r="I44" s="106"/>
-      <c r="J44" s="106"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="105"/>
-      <c r="N44" s="104"/>
-      <c r="O44" s="103"/>
-      <c r="P44" s="102"/>
-      <c r="Q44" s="101"/>
-      <c r="R44" s="100"/>
-      <c r="S44" s="100"/>
+      <c r="A44" s="46"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="85"/>
+      <c r="O44" s="86"/>
+      <c r="P44" s="87"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="72"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
-      <c r="A45" s="101"/>
-      <c r="B45" s="101"/>
-      <c r="C45" s="108"/>
-      <c r="D45" s="108"/>
-      <c r="E45" s="108"/>
-      <c r="F45" s="108"/>
-      <c r="G45" s="108"/>
-      <c r="H45" s="107"/>
-      <c r="I45" s="106"/>
-      <c r="J45" s="106"/>
-      <c r="K45" s="106"/>
-      <c r="L45" s="106"/>
-      <c r="M45" s="105"/>
-      <c r="N45" s="104"/>
-      <c r="O45" s="103"/>
-      <c r="P45" s="102"/>
-      <c r="Q45" s="101"/>
-      <c r="R45" s="100"/>
-      <c r="S45" s="100"/>
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="85"/>
+      <c r="O45" s="86"/>
+      <c r="P45" s="87"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="72"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
-      <c r="A46" s="101"/>
-      <c r="B46" s="101"/>
-      <c r="C46" s="108"/>
-      <c r="D46" s="108"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="107"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="106"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="105"/>
-      <c r="N46" s="104"/>
-      <c r="O46" s="103"/>
-      <c r="P46" s="102"/>
-      <c r="Q46" s="101"/>
-      <c r="R46" s="100"/>
-      <c r="S46" s="100"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
+      <c r="L46" s="57"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="85"/>
+      <c r="O46" s="86"/>
+      <c r="P46" s="87"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="72"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
-      <c r="A47" s="101"/>
-      <c r="B47" s="101"/>
-      <c r="C47" s="108"/>
-      <c r="D47" s="108"/>
-      <c r="E47" s="108"/>
-      <c r="F47" s="108"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="107"/>
-      <c r="I47" s="106"/>
-      <c r="J47" s="106"/>
-      <c r="K47" s="106"/>
-      <c r="L47" s="106"/>
-      <c r="M47" s="105"/>
-      <c r="N47" s="104"/>
-      <c r="O47" s="103"/>
-      <c r="P47" s="102"/>
-      <c r="Q47" s="101"/>
-      <c r="R47" s="100"/>
-      <c r="S47" s="100"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
+      <c r="L47" s="57"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="86"/>
+      <c r="P47" s="87"/>
+      <c r="Q47" s="46"/>
+      <c r="R47" s="72"/>
+      <c r="S47" s="72"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
-      <c r="A48" s="101"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="108"/>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="107"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="106"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="105"/>
-      <c r="N48" s="104"/>
-      <c r="O48" s="103"/>
-      <c r="P48" s="102"/>
-      <c r="Q48" s="101"/>
-      <c r="R48" s="100"/>
-      <c r="S48" s="100"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="85"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="87"/>
+      <c r="Q48" s="46"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="72"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
-      <c r="A49" s="101"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="108"/>
-      <c r="D49" s="108"/>
-      <c r="E49" s="108"/>
-      <c r="F49" s="108"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="107"/>
-      <c r="I49" s="106"/>
-      <c r="J49" s="106"/>
-      <c r="K49" s="106"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="105"/>
-      <c r="N49" s="104"/>
-      <c r="O49" s="103"/>
-      <c r="P49" s="102"/>
-      <c r="Q49" s="101"/>
-      <c r="R49" s="100"/>
-      <c r="S49" s="100"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="57"/>
+      <c r="L49" s="57"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="85"/>
+      <c r="O49" s="86"/>
+      <c r="P49" s="87"/>
+      <c r="Q49" s="46"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="72"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
-      <c r="A50" s="101"/>
-      <c r="B50" s="101"/>
-      <c r="C50" s="108"/>
-      <c r="D50" s="108"/>
-      <c r="E50" s="108"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="107"/>
-      <c r="I50" s="106"/>
-      <c r="J50" s="106"/>
-      <c r="K50" s="106"/>
-      <c r="L50" s="106"/>
-      <c r="M50" s="105"/>
-      <c r="N50" s="104"/>
-      <c r="O50" s="103"/>
-      <c r="P50" s="102"/>
-      <c r="Q50" s="101"/>
-      <c r="R50" s="100"/>
-      <c r="S50" s="100"/>
+      <c r="A50" s="46"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="57"/>
+      <c r="L50" s="57"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="85"/>
+      <c r="O50" s="86"/>
+      <c r="P50" s="87"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="72"/>
+      <c r="S50" s="72"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
-      <c r="A51" s="101"/>
-      <c r="B51" s="101"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="108"/>
-      <c r="E51" s="108"/>
-      <c r="F51" s="108"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="107"/>
-      <c r="I51" s="106"/>
-      <c r="J51" s="106"/>
-      <c r="K51" s="106"/>
-      <c r="L51" s="106"/>
-      <c r="M51" s="105"/>
-      <c r="N51" s="104"/>
-      <c r="O51" s="103"/>
-      <c r="P51" s="102"/>
-      <c r="Q51" s="101"/>
-      <c r="R51" s="100"/>
-      <c r="S51" s="100"/>
+      <c r="A51" s="46"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="85"/>
+      <c r="O51" s="86"/>
+      <c r="P51" s="87"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="72"/>
+      <c r="S51" s="72"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
-      <c r="A52" s="101"/>
-      <c r="B52" s="101"/>
-      <c r="C52" s="108"/>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="107"/>
-      <c r="I52" s="106"/>
-      <c r="J52" s="106"/>
-      <c r="K52" s="106"/>
-      <c r="L52" s="106"/>
-      <c r="M52" s="105"/>
-      <c r="N52" s="104"/>
-      <c r="O52" s="103"/>
-      <c r="P52" s="102"/>
-      <c r="Q52" s="101"/>
-      <c r="R52" s="100"/>
-      <c r="S52" s="100"/>
+      <c r="A52" s="46"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="85"/>
+      <c r="O52" s="86"/>
+      <c r="P52" s="87"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="72"/>
+      <c r="S52" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="H5:M9"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C5:G9"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
     <mergeCell ref="C52:G52"/>
     <mergeCell ref="H52:M52"/>
     <mergeCell ref="C4:G4"/>
@@ -3757,169 +4148,16 @@
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H38:M38"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C5:G9"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="H5:M9"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C47:G47"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -3983,23 +4221,23 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
-      <c r="AO1" s="27" t="s">
+      <c r="AO1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="AP1" s="27"/>
-      <c r="AQ1" s="27"/>
-      <c r="AR1" s="27"/>
-      <c r="AS1" s="27"/>
-      <c r="AT1" s="21">
+      <c r="AP1" s="107"/>
+      <c r="AQ1" s="107"/>
+      <c r="AR1" s="107"/>
+      <c r="AS1" s="107"/>
+      <c r="AT1" s="101">
         <v>46199</v>
       </c>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
-      <c r="AW1" s="22"/>
-      <c r="AX1" s="22"/>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="22"/>
-      <c r="BA1" s="22"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -4045,54 +4283,54 @@
       <c r="AK4" s="8"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="23" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="25"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="105"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="26">
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="106">
         <v>1</v>
       </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="25"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
+      <c r="S6" s="105"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -4101,61 +4339,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="19"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="19"/>
-      <c r="AV9" s="19"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="19"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="20"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+      <c r="AH9" s="99"/>
+      <c r="AI9" s="99"/>
+      <c r="AJ9" s="99"/>
+      <c r="AK9" s="99"/>
+      <c r="AL9" s="99"/>
+      <c r="AM9" s="99"/>
+      <c r="AN9" s="99"/>
+      <c r="AO9" s="99"/>
+      <c r="AP9" s="99"/>
+      <c r="AQ9" s="99"/>
+      <c r="AR9" s="99"/>
+      <c r="AS9" s="99"/>
+      <c r="AT9" s="99"/>
+      <c r="AU9" s="99"/>
+      <c r="AV9" s="99"/>
+      <c r="AW9" s="99"/>
+      <c r="AX9" s="99"/>
+      <c r="AY9" s="99"/>
+      <c r="AZ9" s="99"/>
+      <c r="BA9" s="100"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="10"/>
@@ -7878,61 +8116,61 @@
       <c r="BA102" s="16"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="18" t="s">
+      <c r="A103" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="19"/>
-      <c r="F103" s="19"/>
-      <c r="G103" s="19"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="19"/>
-      <c r="J103" s="19"/>
-      <c r="K103" s="19"/>
-      <c r="L103" s="19"/>
-      <c r="M103" s="19"/>
-      <c r="N103" s="19"/>
-      <c r="O103" s="19"/>
-      <c r="P103" s="19"/>
-      <c r="Q103" s="19"/>
-      <c r="R103" s="19"/>
-      <c r="S103" s="19"/>
-      <c r="T103" s="19"/>
-      <c r="U103" s="19"/>
-      <c r="V103" s="19"/>
-      <c r="W103" s="19"/>
-      <c r="X103" s="19"/>
-      <c r="Y103" s="19"/>
-      <c r="Z103" s="19"/>
-      <c r="AA103" s="19"/>
-      <c r="AB103" s="19"/>
-      <c r="AC103" s="19"/>
-      <c r="AD103" s="19"/>
-      <c r="AE103" s="19"/>
-      <c r="AF103" s="19"/>
-      <c r="AG103" s="19"/>
-      <c r="AH103" s="19"/>
-      <c r="AI103" s="19"/>
-      <c r="AJ103" s="19"/>
-      <c r="AK103" s="19"/>
-      <c r="AL103" s="19"/>
-      <c r="AM103" s="19"/>
-      <c r="AN103" s="19"/>
-      <c r="AO103" s="19"/>
-      <c r="AP103" s="19"/>
-      <c r="AQ103" s="19"/>
-      <c r="AR103" s="19"/>
-      <c r="AS103" s="19"/>
-      <c r="AT103" s="19"/>
-      <c r="AU103" s="19"/>
-      <c r="AV103" s="19"/>
-      <c r="AW103" s="19"/>
-      <c r="AX103" s="19"/>
-      <c r="AY103" s="19"/>
-      <c r="AZ103" s="19"/>
-      <c r="BA103" s="20"/>
+      <c r="B103" s="99"/>
+      <c r="C103" s="99"/>
+      <c r="D103" s="99"/>
+      <c r="E103" s="99"/>
+      <c r="F103" s="99"/>
+      <c r="G103" s="99"/>
+      <c r="H103" s="99"/>
+      <c r="I103" s="99"/>
+      <c r="J103" s="99"/>
+      <c r="K103" s="99"/>
+      <c r="L103" s="99"/>
+      <c r="M103" s="99"/>
+      <c r="N103" s="99"/>
+      <c r="O103" s="99"/>
+      <c r="P103" s="99"/>
+      <c r="Q103" s="99"/>
+      <c r="R103" s="99"/>
+      <c r="S103" s="99"/>
+      <c r="T103" s="99"/>
+      <c r="U103" s="99"/>
+      <c r="V103" s="99"/>
+      <c r="W103" s="99"/>
+      <c r="X103" s="99"/>
+      <c r="Y103" s="99"/>
+      <c r="Z103" s="99"/>
+      <c r="AA103" s="99"/>
+      <c r="AB103" s="99"/>
+      <c r="AC103" s="99"/>
+      <c r="AD103" s="99"/>
+      <c r="AE103" s="99"/>
+      <c r="AF103" s="99"/>
+      <c r="AG103" s="99"/>
+      <c r="AH103" s="99"/>
+      <c r="AI103" s="99"/>
+      <c r="AJ103" s="99"/>
+      <c r="AK103" s="99"/>
+      <c r="AL103" s="99"/>
+      <c r="AM103" s="99"/>
+      <c r="AN103" s="99"/>
+      <c r="AO103" s="99"/>
+      <c r="AP103" s="99"/>
+      <c r="AQ103" s="99"/>
+      <c r="AR103" s="99"/>
+      <c r="AS103" s="99"/>
+      <c r="AT103" s="99"/>
+      <c r="AU103" s="99"/>
+      <c r="AV103" s="99"/>
+      <c r="AW103" s="99"/>
+      <c r="AX103" s="99"/>
+      <c r="AY103" s="99"/>
+      <c r="AZ103" s="99"/>
+      <c r="BA103" s="100"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="12"/>
@@ -8255,61 +8493,61 @@
       <c r="BA111" s="16"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="18" t="s">
+      <c r="A112" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="19"/>
-      <c r="H112" s="19"/>
-      <c r="I112" s="19"/>
-      <c r="J112" s="19"/>
-      <c r="K112" s="19"/>
-      <c r="L112" s="19"/>
-      <c r="M112" s="19"/>
-      <c r="N112" s="19"/>
-      <c r="O112" s="19"/>
-      <c r="P112" s="19"/>
-      <c r="Q112" s="19"/>
-      <c r="R112" s="19"/>
-      <c r="S112" s="19"/>
-      <c r="T112" s="19"/>
-      <c r="U112" s="19"/>
-      <c r="V112" s="19"/>
-      <c r="W112" s="19"/>
-      <c r="X112" s="19"/>
-      <c r="Y112" s="19"/>
-      <c r="Z112" s="19"/>
-      <c r="AA112" s="19"/>
-      <c r="AB112" s="19"/>
-      <c r="AC112" s="19"/>
-      <c r="AD112" s="19"/>
-      <c r="AE112" s="19"/>
-      <c r="AF112" s="19"/>
-      <c r="AG112" s="19"/>
-      <c r="AH112" s="19"/>
-      <c r="AI112" s="19"/>
-      <c r="AJ112" s="19"/>
-      <c r="AK112" s="19"/>
-      <c r="AL112" s="19"/>
-      <c r="AM112" s="19"/>
-      <c r="AN112" s="19"/>
-      <c r="AO112" s="19"/>
-      <c r="AP112" s="19"/>
-      <c r="AQ112" s="19"/>
-      <c r="AR112" s="19"/>
-      <c r="AS112" s="19"/>
-      <c r="AT112" s="19"/>
-      <c r="AU112" s="19"/>
-      <c r="AV112" s="19"/>
-      <c r="AW112" s="19"/>
-      <c r="AX112" s="19"/>
-      <c r="AY112" s="19"/>
-      <c r="AZ112" s="19"/>
-      <c r="BA112" s="19"/>
+      <c r="B112" s="99"/>
+      <c r="C112" s="99"/>
+      <c r="D112" s="99"/>
+      <c r="E112" s="99"/>
+      <c r="F112" s="99"/>
+      <c r="G112" s="99"/>
+      <c r="H112" s="99"/>
+      <c r="I112" s="99"/>
+      <c r="J112" s="99"/>
+      <c r="K112" s="99"/>
+      <c r="L112" s="99"/>
+      <c r="M112" s="99"/>
+      <c r="N112" s="99"/>
+      <c r="O112" s="99"/>
+      <c r="P112" s="99"/>
+      <c r="Q112" s="99"/>
+      <c r="R112" s="99"/>
+      <c r="S112" s="99"/>
+      <c r="T112" s="99"/>
+      <c r="U112" s="99"/>
+      <c r="V112" s="99"/>
+      <c r="W112" s="99"/>
+      <c r="X112" s="99"/>
+      <c r="Y112" s="99"/>
+      <c r="Z112" s="99"/>
+      <c r="AA112" s="99"/>
+      <c r="AB112" s="99"/>
+      <c r="AC112" s="99"/>
+      <c r="AD112" s="99"/>
+      <c r="AE112" s="99"/>
+      <c r="AF112" s="99"/>
+      <c r="AG112" s="99"/>
+      <c r="AH112" s="99"/>
+      <c r="AI112" s="99"/>
+      <c r="AJ112" s="99"/>
+      <c r="AK112" s="99"/>
+      <c r="AL112" s="99"/>
+      <c r="AM112" s="99"/>
+      <c r="AN112" s="99"/>
+      <c r="AO112" s="99"/>
+      <c r="AP112" s="99"/>
+      <c r="AQ112" s="99"/>
+      <c r="AR112" s="99"/>
+      <c r="AS112" s="99"/>
+      <c r="AT112" s="99"/>
+      <c r="AU112" s="99"/>
+      <c r="AV112" s="99"/>
+      <c r="AW112" s="99"/>
+      <c r="AX112" s="99"/>
+      <c r="AY112" s="99"/>
+      <c r="AZ112" s="99"/>
+      <c r="BA112" s="99"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="12"/>
@@ -8476,1003 +8714,1003 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="6" width="2.5" style="28" customWidth="1"/>
-    <col min="7" max="17" width="7.125" style="28" customWidth="1"/>
-    <col min="18" max="18" width="9" style="28" customWidth="1"/>
-    <col min="19" max="20" width="7.125" style="28" customWidth="1"/>
-    <col min="21" max="26" width="7.625" style="28" customWidth="1"/>
-    <col min="27" max="16384" width="12.625" style="28"/>
+    <col min="1" max="6" width="2.5" style="18" customWidth="1"/>
+    <col min="7" max="17" width="7.125" style="18" customWidth="1"/>
+    <col min="18" max="18" width="9" style="18" customWidth="1"/>
+    <col min="19" max="20" width="7.125" style="18" customWidth="1"/>
+    <col min="21" max="26" width="7.625" style="18" customWidth="1"/>
+    <col min="27" max="16384" width="12.625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="142" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="94" t="s">
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="94" t="s">
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="94" t="s">
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="147" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="94" t="s">
+      <c r="P1" s="133"/>
+      <c r="Q1" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="R1" s="77"/>
-      <c r="S1" s="94" t="s">
+      <c r="R1" s="133"/>
+      <c r="S1" s="147" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="74"/>
+      <c r="T1" s="135"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="88"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="90" t="s">
+      <c r="A2" s="145"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="90" t="s">
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="92">
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="138">
         <v>46199</v>
       </c>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="90" t="s">
+      <c r="P2" s="124"/>
+      <c r="Q2" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="91"/>
-      <c r="S2" s="90"/>
-      <c r="T2" s="89"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="139"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="88"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="84"/>
+      <c r="A3" s="145"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="140"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="81"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="81"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="79"/>
+      <c r="A4" s="146"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="128"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="128"/>
+      <c r="T4" s="141"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="76" t="s">
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="74"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="132"/>
+      <c r="T5" s="135"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="73" t="s">
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="72"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="115"/>
+      <c r="T6" s="137"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="73" t="s">
+      <c r="B7" s="115"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="72"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="115"/>
+      <c r="M7" s="115"/>
+      <c r="N7" s="115"/>
+      <c r="O7" s="115"/>
+      <c r="P7" s="115"/>
+      <c r="Q7" s="115"/>
+      <c r="R7" s="115"/>
+      <c r="S7" s="115"/>
+      <c r="T7" s="137"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="59"/>
-      <c r="S8" s="59"/>
-      <c r="T8" s="58"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="30"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="66"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="71" t="s">
+      <c r="A9" s="38"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="70"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="61"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="61"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="61"/>
-      <c r="S9" s="61"/>
-      <c r="T9" s="62"/>
-      <c r="U9" s="61"/>
-      <c r="V9" s="61"/>
-      <c r="W9" s="61"/>
-      <c r="X9" s="61"/>
-      <c r="Y9" s="61"/>
-      <c r="Z9" s="61"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="33"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="66"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="61"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="61"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="61"/>
-      <c r="V10" s="61"/>
-      <c r="W10" s="61"/>
-      <c r="X10" s="61"/>
-      <c r="Y10" s="61"/>
-      <c r="Z10" s="61"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="33"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="66"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="61"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="62"/>
-      <c r="U11" s="61"/>
-      <c r="V11" s="61"/>
-      <c r="W11" s="61"/>
-      <c r="X11" s="61"/>
-      <c r="Y11" s="61"/>
-      <c r="Z11" s="61"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="33"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="66"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61" t="s">
+      <c r="A12" s="38"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="61"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
-      <c r="O12" s="61"/>
-      <c r="P12" s="61"/>
-      <c r="Q12" s="61"/>
-      <c r="R12" s="61"/>
-      <c r="S12" s="61"/>
-      <c r="T12" s="62"/>
-      <c r="U12" s="61"/>
-      <c r="V12" s="61"/>
-      <c r="W12" s="61"/>
-      <c r="X12" s="61"/>
-      <c r="Y12" s="61"/>
-      <c r="Z12" s="61"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="66"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64" t="s">
+      <c r="A13" s="38"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="64"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="61"/>
-      <c r="V13" s="61"/>
-      <c r="W13" s="61"/>
-      <c r="X13" s="61"/>
-      <c r="Y13" s="61"/>
-      <c r="Z13" s="61"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="33"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="59"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="58"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="30"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="56" t="s">
+      <c r="B15" s="109"/>
+      <c r="C15" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="55" t="s">
+      <c r="D15" s="109"/>
+      <c r="E15" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="55" t="s">
+      <c r="F15" s="109"/>
+      <c r="G15" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="55" t="s">
+      <c r="H15" s="115"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="55" t="s">
+      <c r="K15" s="109"/>
+      <c r="L15" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="55" t="s">
+      <c r="M15" s="115"/>
+      <c r="N15" s="109"/>
+      <c r="O15" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="54" t="s">
+      <c r="P15" s="115"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="S15" s="54" t="s">
+      <c r="S15" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="T15" s="53" t="s">
+      <c r="T15" s="28" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="46">
+      <c r="A16" s="110">
         <v>1</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="45" t="s">
+      <c r="B16" s="109"/>
+      <c r="C16" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="45" t="s">
+      <c r="D16" s="109"/>
+      <c r="E16" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="44" t="s">
+      <c r="F16" s="109"/>
+      <c r="G16" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="44" t="s">
+      <c r="H16" s="115"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="43" t="s">
+      <c r="K16" s="109"/>
+      <c r="L16" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="43" t="s">
+      <c r="M16" s="115"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="49">
+      <c r="P16" s="115"/>
+      <c r="Q16" s="109"/>
+      <c r="R16" s="27">
         <v>46199</v>
       </c>
-      <c r="S16" s="48" t="s">
+      <c r="S16" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="T16" s="47" t="s">
+      <c r="T16" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
     </row>
     <row r="17" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A17" s="46">
+      <c r="A17" s="110">
         <v>2</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="45" t="s">
+      <c r="B17" s="109"/>
+      <c r="C17" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="45" t="s">
+      <c r="D17" s="109"/>
+      <c r="E17" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="41"/>
-      <c r="G17" s="52" t="s">
+      <c r="F17" s="109"/>
+      <c r="G17" s="149" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="44" t="s">
+      <c r="H17" s="150"/>
+      <c r="I17" s="151"/>
+      <c r="J17" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="41"/>
-      <c r="L17" s="43" t="s">
+      <c r="K17" s="109"/>
+      <c r="L17" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="43" t="s">
+      <c r="M17" s="115"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="49">
+      <c r="P17" s="115"/>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="27">
         <v>46199</v>
       </c>
-      <c r="S17" s="48" t="s">
+      <c r="S17" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="T17" s="47" t="s">
+      <c r="T17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
     </row>
     <row r="18" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="110">
         <v>3</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="45" t="s">
+      <c r="B18" s="109"/>
+      <c r="C18" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="45" t="s">
+      <c r="D18" s="109"/>
+      <c r="E18" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="44" t="s">
+      <c r="F18" s="109"/>
+      <c r="G18" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="44" t="s">
+      <c r="H18" s="115"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="41"/>
-      <c r="L18" s="43" t="s">
+      <c r="K18" s="109"/>
+      <c r="L18" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="42"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="43" t="s">
+      <c r="M18" s="115"/>
+      <c r="N18" s="109"/>
+      <c r="O18" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="49">
+      <c r="P18" s="115"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="27">
         <v>46199</v>
       </c>
-      <c r="S18" s="48" t="s">
+      <c r="S18" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="T18" s="47" t="s">
+      <c r="T18" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
     </row>
     <row r="19" spans="1:26" ht="51.75" customHeight="1">
-      <c r="A19" s="46">
+      <c r="A19" s="110">
         <v>4</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="45" t="s">
+      <c r="B19" s="109"/>
+      <c r="C19" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="45" t="s">
+      <c r="D19" s="109"/>
+      <c r="E19" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="44" t="s">
+      <c r="F19" s="109"/>
+      <c r="G19" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="44" t="s">
+      <c r="H19" s="115"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="41"/>
-      <c r="L19" s="43" t="s">
+      <c r="K19" s="109"/>
+      <c r="L19" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="M19" s="42"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="43" t="s">
+      <c r="M19" s="115"/>
+      <c r="N19" s="109"/>
+      <c r="O19" s="114" t="s">
         <v>18</v>
       </c>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="49">
+      <c r="P19" s="115"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="27">
         <v>46199</v>
       </c>
-      <c r="S19" s="48" t="s">
+      <c r="S19" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="T19" s="47" t="s">
+      <c r="T19" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
     </row>
     <row r="20" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A20" s="46">
+      <c r="A20" s="110">
         <v>5</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="45" t="s">
+      <c r="B20" s="109"/>
+      <c r="C20" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="45" t="s">
+      <c r="D20" s="109"/>
+      <c r="E20" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="44" t="s">
+      <c r="F20" s="109"/>
+      <c r="G20" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="44" t="s">
+      <c r="H20" s="115"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="K20" s="41"/>
-      <c r="L20" s="43" t="s">
+      <c r="K20" s="109"/>
+      <c r="L20" s="114" t="s">
         <v>14</v>
       </c>
-      <c r="M20" s="42"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="43" t="s">
+      <c r="M20" s="115"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="49">
+      <c r="P20" s="115"/>
+      <c r="Q20" s="109"/>
+      <c r="R20" s="27">
         <v>46199</v>
       </c>
-      <c r="S20" s="48" t="s">
+      <c r="S20" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="T20" s="47" t="s">
+      <c r="T20" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
     </row>
     <row r="21" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A21" s="46"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="40"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="39"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="24"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="46"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="39"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
+      <c r="A22" s="110"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="39"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="109"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="109"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="109"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="115"/>
+      <c r="Q23" s="109"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="46"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
+      <c r="A24" s="110"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="109"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="115"/>
+      <c r="N24" s="109"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="115"/>
+      <c r="Q24" s="109"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="24"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="46"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="39"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="115"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="115"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="39"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
+      <c r="A26" s="110"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="109"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="109"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="115"/>
+      <c r="N26" s="109"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="115"/>
+      <c r="Q26" s="109"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="39"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
+      <c r="A27" s="110"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="109"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="115"/>
+      <c r="Q27" s="109"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="46"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="40"/>
-      <c r="S28" s="40"/>
-      <c r="T28" s="39"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
+      <c r="A28" s="110"/>
+      <c r="B28" s="109"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="109"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="109"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="109"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="115"/>
+      <c r="Q28" s="109"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="46"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="39"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
+      <c r="A29" s="110"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="115"/>
+      <c r="N29" s="109"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="115"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="46"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="39"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
+      <c r="A30" s="110"/>
+      <c r="B30" s="109"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="115"/>
+      <c r="N30" s="109"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="115"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="24"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="38"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
+      <c r="A31" s="111"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="148"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="117"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="117"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
     </row>
     <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
@@ -9489,1016 +9727,1009 @@
     <row r="46" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="47" spans="4:10" ht="12.75" customHeight="1"/>
     <row r="48" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="49" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" s="28" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" s="28" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="49" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" s="18" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" s="18" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="L15:N15"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="L16:N16"/>
@@ -10516,69 +10747,76 @@
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G16:I16"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10641,23 +10879,23 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
-      <c r="AO1" s="27" t="s">
+      <c r="AO1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="AP1" s="27"/>
-      <c r="AQ1" s="27"/>
-      <c r="AR1" s="27"/>
-      <c r="AS1" s="27"/>
-      <c r="AT1" s="21">
+      <c r="AP1" s="107"/>
+      <c r="AQ1" s="107"/>
+      <c r="AR1" s="107"/>
+      <c r="AS1" s="107"/>
+      <c r="AT1" s="101">
         <v>44861</v>
       </c>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
-      <c r="AW1" s="22"/>
-      <c r="AX1" s="22"/>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="22"/>
-      <c r="BA1" s="22"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -10703,54 +10941,54 @@
       <c r="AK4" s="8"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="23" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="25"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="105"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="26">
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="106">
         <v>1</v>
       </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="25"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
+      <c r="S6" s="105"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -10759,61 +10997,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="19"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="19"/>
-      <c r="AV9" s="19"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="19"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="20"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+      <c r="AH9" s="99"/>
+      <c r="AI9" s="99"/>
+      <c r="AJ9" s="99"/>
+      <c r="AK9" s="99"/>
+      <c r="AL9" s="99"/>
+      <c r="AM9" s="99"/>
+      <c r="AN9" s="99"/>
+      <c r="AO9" s="99"/>
+      <c r="AP9" s="99"/>
+      <c r="AQ9" s="99"/>
+      <c r="AR9" s="99"/>
+      <c r="AS9" s="99"/>
+      <c r="AT9" s="99"/>
+      <c r="AU9" s="99"/>
+      <c r="AV9" s="99"/>
+      <c r="AW9" s="99"/>
+      <c r="AX9" s="99"/>
+      <c r="AY9" s="99"/>
+      <c r="AZ9" s="99"/>
+      <c r="BA9" s="100"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="10"/>
@@ -11776,61 +12014,61 @@
       <c r="BA33" s="16"/>
     </row>
     <row r="34" spans="1:53" ht="18" customHeight="1">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="19"/>
-      <c r="Z34" s="19"/>
-      <c r="AA34" s="19"/>
-      <c r="AB34" s="19"/>
-      <c r="AC34" s="19"/>
-      <c r="AD34" s="19"/>
-      <c r="AE34" s="19"/>
-      <c r="AF34" s="19"/>
-      <c r="AG34" s="19"/>
-      <c r="AH34" s="19"/>
-      <c r="AI34" s="19"/>
-      <c r="AJ34" s="19"/>
-      <c r="AK34" s="19"/>
-      <c r="AL34" s="19"/>
-      <c r="AM34" s="19"/>
-      <c r="AN34" s="19"/>
-      <c r="AO34" s="19"/>
-      <c r="AP34" s="19"/>
-      <c r="AQ34" s="19"/>
-      <c r="AR34" s="19"/>
-      <c r="AS34" s="19"/>
-      <c r="AT34" s="19"/>
-      <c r="AU34" s="19"/>
-      <c r="AV34" s="19"/>
-      <c r="AW34" s="19"/>
-      <c r="AX34" s="19"/>
-      <c r="AY34" s="19"/>
-      <c r="AZ34" s="19"/>
-      <c r="BA34" s="20"/>
+      <c r="B34" s="99"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="99"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="99"/>
+      <c r="R34" s="99"/>
+      <c r="S34" s="99"/>
+      <c r="T34" s="99"/>
+      <c r="U34" s="99"/>
+      <c r="V34" s="99"/>
+      <c r="W34" s="99"/>
+      <c r="X34" s="99"/>
+      <c r="Y34" s="99"/>
+      <c r="Z34" s="99"/>
+      <c r="AA34" s="99"/>
+      <c r="AB34" s="99"/>
+      <c r="AC34" s="99"/>
+      <c r="AD34" s="99"/>
+      <c r="AE34" s="99"/>
+      <c r="AF34" s="99"/>
+      <c r="AG34" s="99"/>
+      <c r="AH34" s="99"/>
+      <c r="AI34" s="99"/>
+      <c r="AJ34" s="99"/>
+      <c r="AK34" s="99"/>
+      <c r="AL34" s="99"/>
+      <c r="AM34" s="99"/>
+      <c r="AN34" s="99"/>
+      <c r="AO34" s="99"/>
+      <c r="AP34" s="99"/>
+      <c r="AQ34" s="99"/>
+      <c r="AR34" s="99"/>
+      <c r="AS34" s="99"/>
+      <c r="AT34" s="99"/>
+      <c r="AU34" s="99"/>
+      <c r="AV34" s="99"/>
+      <c r="AW34" s="99"/>
+      <c r="AX34" s="99"/>
+      <c r="AY34" s="99"/>
+      <c r="AZ34" s="99"/>
+      <c r="BA34" s="100"/>
     </row>
     <row r="35" spans="1:53" ht="21.95" customHeight="1">
       <c r="A35" s="12"/>
@@ -12153,61 +12391,61 @@
       <c r="BA42" s="16"/>
     </row>
     <row r="43" spans="1:53" ht="18" customHeight="1">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="19"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="19"/>
-      <c r="W43" s="19"/>
-      <c r="X43" s="19"/>
-      <c r="Y43" s="19"/>
-      <c r="Z43" s="19"/>
-      <c r="AA43" s="19"/>
-      <c r="AB43" s="19"/>
-      <c r="AC43" s="19"/>
-      <c r="AD43" s="19"/>
-      <c r="AE43" s="19"/>
-      <c r="AF43" s="19"/>
-      <c r="AG43" s="19"/>
-      <c r="AH43" s="19"/>
-      <c r="AI43" s="19"/>
-      <c r="AJ43" s="19"/>
-      <c r="AK43" s="19"/>
-      <c r="AL43" s="19"/>
-      <c r="AM43" s="19"/>
-      <c r="AN43" s="19"/>
-      <c r="AO43" s="19"/>
-      <c r="AP43" s="19"/>
-      <c r="AQ43" s="19"/>
-      <c r="AR43" s="19"/>
-      <c r="AS43" s="19"/>
-      <c r="AT43" s="19"/>
-      <c r="AU43" s="19"/>
-      <c r="AV43" s="19"/>
-      <c r="AW43" s="19"/>
-      <c r="AX43" s="19"/>
-      <c r="AY43" s="19"/>
-      <c r="AZ43" s="19"/>
-      <c r="BA43" s="19"/>
+      <c r="B43" s="99"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="99"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="99"/>
+      <c r="AB43" s="99"/>
+      <c r="AC43" s="99"/>
+      <c r="AD43" s="99"/>
+      <c r="AE43" s="99"/>
+      <c r="AF43" s="99"/>
+      <c r="AG43" s="99"/>
+      <c r="AH43" s="99"/>
+      <c r="AI43" s="99"/>
+      <c r="AJ43" s="99"/>
+      <c r="AK43" s="99"/>
+      <c r="AL43" s="99"/>
+      <c r="AM43" s="99"/>
+      <c r="AN43" s="99"/>
+      <c r="AO43" s="99"/>
+      <c r="AP43" s="99"/>
+      <c r="AQ43" s="99"/>
+      <c r="AR43" s="99"/>
+      <c r="AS43" s="99"/>
+      <c r="AT43" s="99"/>
+      <c r="AU43" s="99"/>
+      <c r="AV43" s="99"/>
+      <c r="AW43" s="99"/>
+      <c r="AX43" s="99"/>
+      <c r="AY43" s="99"/>
+      <c r="AZ43" s="99"/>
+      <c r="BA43" s="99"/>
     </row>
     <row r="44" spans="1:53" ht="21.95" customHeight="1">
       <c r="A44" s="12"/>
@@ -12367,4 +12605,1338 @@
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC38BB8E-D2DB-44C4-875D-CD450D3627F9}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="11.875" style="44" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="45" customWidth="1"/>
+    <col min="3" max="6" width="7.125" style="44" customWidth="1"/>
+    <col min="7" max="7" width="7.125" style="45" customWidth="1"/>
+    <col min="8" max="13" width="7.125" style="44" customWidth="1"/>
+    <col min="14" max="19" width="10.625" style="44" customWidth="1"/>
+    <col min="20" max="16384" width="7" style="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="O1" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="R1" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="S1" s="79"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="75"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="94">
+        <v>46202</v>
+      </c>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="156"/>
+      <c r="S2" s="97"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="R4" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="S4" s="62"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="49"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="154"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="84"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="46">
+        <v>1</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="91" t="s">
+        <v>112</v>
+      </c>
+      <c r="O6" s="92"/>
+      <c r="P6" s="93"/>
+      <c r="Q6" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+    </row>
+    <row r="8" spans="1:19" ht="42.75" customHeight="1">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="O8" s="86"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="59"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="86"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="46"/>
+      <c r="B10" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="O10" s="86"/>
+      <c r="P10" s="87"/>
+      <c r="Q10" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="86"/>
+      <c r="P11" s="87"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="46"/>
+      <c r="B12" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="O12" s="86"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R12" s="63"/>
+      <c r="S12" s="65"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+    </row>
+    <row r="14" spans="1:19" ht="37.5" customHeight="1">
+      <c r="A14" s="46">
+        <v>2</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="153" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="85" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="86"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="46"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="46">
+        <v>3</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="O16" s="86"/>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="46">
+        <v>4</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="85" t="s">
+        <v>92</v>
+      </c>
+      <c r="O18" s="86"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="47">
+        <v>46202</v>
+      </c>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="86"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="86"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="152"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="87"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="86"/>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="87"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="87"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="86"/>
+      <c r="P27" s="87"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="87"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="87"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="87"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="86"/>
+      <c r="P31" s="87"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="86"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="87"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="72"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="46"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="85"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="87"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="46"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="72"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="46"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="87"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="46"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="86"/>
+      <c r="P37" s="87"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="72"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="46"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="86"/>
+      <c r="P38" s="87"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="72"/>
+      <c r="S38" s="72"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="46"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="86"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="72"/>
+      <c r="S39" s="72"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="46"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="85"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="87"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="72"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="46"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="85"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="72"/>
+      <c r="S41" s="72"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="58"/>
+      <c r="N42" s="85"/>
+      <c r="O42" s="86"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="72"/>
+      <c r="S42" s="72"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="85"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="87"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="72"/>
+      <c r="S43" s="72"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="46"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="85"/>
+      <c r="O44" s="86"/>
+      <c r="P44" s="87"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="72"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="85"/>
+      <c r="O45" s="86"/>
+      <c r="P45" s="87"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="72"/>
+      <c r="S45" s="72"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
+      <c r="L46" s="57"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="85"/>
+      <c r="O46" s="86"/>
+      <c r="P46" s="87"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="72"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
+      <c r="L47" s="57"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="86"/>
+      <c r="P47" s="87"/>
+      <c r="Q47" s="46"/>
+      <c r="R47" s="72"/>
+      <c r="S47" s="72"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="72"/>
+    </row>
+    <row r="49" spans="3:7" ht="30" customHeight="1">
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+    </row>
+    <row r="50" spans="3:7" ht="30" customHeight="1"/>
+    <row r="51" spans="3:7" ht="30" customHeight="1"/>
+    <row r="52" spans="3:7" ht="30" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="188">
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>
--- a/document/タスク一覧表示機能テスト.xlsx
+++ b/document/タスク一覧表示機能テスト.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176BD691-D9D0-4AF6-8914-2A2EC7EF770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C8D3FD-0164-4A54-9F69-381908056819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="270" windowWidth="17910" windowHeight="9975" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="4" r:id="rId1"/>
@@ -14,9 +14,6 @@
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId4"/>
     <sheet name="テスト仕様書兼報告書" sheetId="5" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <definedNames>
     <definedName name="範囲１" localSheetId="0">#REF!</definedName>
     <definedName name="範囲１" localSheetId="4">#REF!</definedName>
@@ -27,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="120">
   <si>
     <t>（１）概要</t>
     <rPh sb="3" eb="5">
@@ -1966,6 +1963,18 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1975,123 +1984,126 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2122,152 +2134,137 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="9" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2473,29 +2470,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="サンプル"/>
-      <sheetName val="テストケースに記載する要素"/>
-      <sheetName val="テスト用語"/>
-      <sheetName val="テスト観点一覧"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2774,72 +2748,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="79"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="64"/>
       <c r="N1" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="O1" s="77" t="s">
+      <c r="O1" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="79"/>
+      <c r="P1" s="64"/>
       <c r="Q1" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="R1" s="77" t="s">
+      <c r="R1" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="79"/>
+      <c r="S1" s="64"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="74" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="75"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="77" t="s">
+      <c r="D2" s="87"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="79"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="64"/>
       <c r="N2" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="94">
+      <c r="O2" s="65">
         <v>46199</v>
       </c>
-      <c r="P2" s="95"/>
+      <c r="P2" s="66"/>
       <c r="Q2" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="96">
+      <c r="R2" s="101">
         <v>44771</v>
       </c>
-      <c r="S2" s="97"/>
+      <c r="S2" s="82"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="53"/>
@@ -2869,33 +2843,33 @@
       <c r="B4" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="60" t="s">
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="60" t="s">
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="61"/>
-      <c r="P4" s="62"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="71"/>
       <c r="Q4" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="R4" s="60" t="s">
+      <c r="R4" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="S4" s="62"/>
+      <c r="S4" s="71"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="49">
@@ -2904,33 +2878,33 @@
       <c r="B5" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="66" t="s">
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="88" t="s">
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="O5" s="89"/>
-      <c r="P5" s="90"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="74"/>
       <c r="Q5" s="48">
         <v>46198</v>
       </c>
-      <c r="R5" s="83" t="s">
+      <c r="R5" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="S5" s="84"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="46">
@@ -2939,29 +2913,29 @@
       <c r="B6" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="91" t="s">
+      <c r="C6" s="95"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="92"/>
-      <c r="P6" s="93"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="76"/>
       <c r="Q6" s="48">
         <v>46198</v>
       </c>
-      <c r="R6" s="72" t="s">
+      <c r="R6" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="S6" s="72"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="46">
@@ -2970,29 +2944,29 @@
       <c r="B7" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="85" t="s">
+      <c r="C7" s="95"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="O7" s="86"/>
-      <c r="P7" s="87"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="59"/>
       <c r="Q7" s="48">
         <v>46198</v>
       </c>
-      <c r="R7" s="72" t="s">
+      <c r="R7" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="S7" s="72"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="46">
@@ -3001,29 +2975,29 @@
       <c r="B8" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="85" t="s">
+      <c r="C8" s="95"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="86"/>
-      <c r="P8" s="87"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="59"/>
       <c r="Q8" s="48">
         <v>46198</v>
       </c>
-      <c r="R8" s="72" t="s">
+      <c r="R8" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="S8" s="72"/>
+      <c r="S8" s="68"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="46">
@@ -3032,1098 +3006,945 @@
       <c r="B9" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="85" t="s">
+      <c r="C9" s="95"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="O9" s="86"/>
-      <c r="P9" s="87"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="59"/>
       <c r="Q9" s="48">
         <v>46198</v>
       </c>
-      <c r="R9" s="72" t="s">
+      <c r="R9" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="S9" s="72"/>
+      <c r="S9" s="68"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="46"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="87"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="59"/>
       <c r="Q10" s="47"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="46"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="86"/>
-      <c r="P11" s="87"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="59"/>
       <c r="Q11" s="46"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="46"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="87"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="59"/>
       <c r="Q12" s="46"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="72"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="46"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="87"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="59"/>
       <c r="Q13" s="46"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="46"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="86"/>
-      <c r="P14" s="87"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="59"/>
       <c r="Q14" s="46"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="87"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="59"/>
       <c r="Q15" s="46"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="46"/>
       <c r="B16" s="46"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="86"/>
-      <c r="P16" s="87"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="59"/>
       <c r="Q16" s="46"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
+      <c r="R16" s="68"/>
+      <c r="S16" s="68"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="46"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="86"/>
-      <c r="P17" s="87"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="59"/>
       <c r="Q17" s="46"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="68"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="46"/>
       <c r="B18" s="46"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="87"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="59"/>
       <c r="Q18" s="46"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="46"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="86"/>
-      <c r="P19" s="87"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="59"/>
       <c r="Q19" s="46"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="46"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="86"/>
-      <c r="P20" s="87"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="59"/>
       <c r="Q20" s="46"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="86"/>
-      <c r="P21" s="87"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="59"/>
       <c r="Q21" s="46"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="87"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="59"/>
       <c r="Q22" s="46"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="68"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="86"/>
-      <c r="P23" s="87"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="59"/>
       <c r="Q23" s="46"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="87"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="59"/>
       <c r="Q24" s="46"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
+      <c r="R24" s="68"/>
+      <c r="S24" s="68"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="46"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="87"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="59"/>
       <c r="Q25" s="46"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="68"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="86"/>
-      <c r="P26" s="87"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="59"/>
       <c r="Q26" s="46"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="72"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="46"/>
       <c r="B27" s="46"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="86"/>
-      <c r="P27" s="87"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="59"/>
       <c r="Q27" s="46"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="72"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="68"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="46"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="87"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="59"/>
       <c r="Q28" s="46"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="46"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="87"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="59"/>
       <c r="Q29" s="46"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="72"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="46"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="87"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="59"/>
       <c r="Q30" s="46"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="72"/>
+      <c r="R30" s="68"/>
+      <c r="S30" s="68"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="86"/>
-      <c r="P31" s="87"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="59"/>
       <c r="Q31" s="46"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
+      <c r="R31" s="68"/>
+      <c r="S31" s="68"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="86"/>
-      <c r="P32" s="87"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="59"/>
       <c r="Q32" s="46"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="72"/>
+      <c r="R32" s="68"/>
+      <c r="S32" s="68"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="87"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="59"/>
       <c r="Q33" s="46"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="72"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="85"/>
-      <c r="O34" s="86"/>
-      <c r="P34" s="87"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="59"/>
       <c r="Q34" s="46"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="72"/>
+      <c r="R34" s="68"/>
+      <c r="S34" s="68"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="85"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="87"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="57"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="59"/>
       <c r="Q35" s="46"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
+      <c r="R35" s="68"/>
+      <c r="S35" s="68"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="86"/>
-      <c r="P36" s="87"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="59"/>
       <c r="Q36" s="46"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="68"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="46"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="58"/>
-      <c r="N37" s="85"/>
-      <c r="O37" s="86"/>
-      <c r="P37" s="87"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="59"/>
       <c r="Q37" s="46"/>
-      <c r="R37" s="72"/>
-      <c r="S37" s="72"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="68"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="85"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="87"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="59"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="72"/>
-      <c r="S38" s="72"/>
+      <c r="R38" s="68"/>
+      <c r="S38" s="68"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="58"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="86"/>
-      <c r="P39" s="87"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="59"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="72"/>
-      <c r="S39" s="72"/>
+      <c r="R39" s="68"/>
+      <c r="S39" s="68"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="85"/>
-      <c r="O40" s="86"/>
-      <c r="P40" s="87"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="59"/>
       <c r="Q40" s="46"/>
-      <c r="R40" s="72"/>
-      <c r="S40" s="72"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="68"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="85"/>
-      <c r="O41" s="86"/>
-      <c r="P41" s="87"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="61"/>
+      <c r="M41" s="62"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="59"/>
       <c r="Q41" s="46"/>
-      <c r="R41" s="72"/>
-      <c r="S41" s="72"/>
+      <c r="R41" s="68"/>
+      <c r="S41" s="68"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="46"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="58"/>
-      <c r="N42" s="85"/>
-      <c r="O42" s="86"/>
-      <c r="P42" s="87"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="62"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="59"/>
       <c r="Q42" s="46"/>
-      <c r="R42" s="72"/>
-      <c r="S42" s="72"/>
+      <c r="R42" s="68"/>
+      <c r="S42" s="68"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="46"/>
       <c r="B43" s="46"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="58"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="86"/>
-      <c r="P43" s="87"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
+      <c r="L43" s="61"/>
+      <c r="M43" s="62"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="59"/>
       <c r="Q43" s="46"/>
-      <c r="R43" s="72"/>
-      <c r="S43" s="72"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="68"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="58"/>
-      <c r="N44" s="85"/>
-      <c r="O44" s="86"/>
-      <c r="P44" s="87"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="61"/>
+      <c r="J44" s="61"/>
+      <c r="K44" s="61"/>
+      <c r="L44" s="61"/>
+      <c r="M44" s="62"/>
+      <c r="N44" s="57"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="59"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="72"/>
-      <c r="S44" s="72"/>
+      <c r="R44" s="68"/>
+      <c r="S44" s="68"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="46"/>
       <c r="B45" s="46"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="85"/>
-      <c r="O45" s="86"/>
-      <c r="P45" s="87"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="61"/>
+      <c r="L45" s="61"/>
+      <c r="M45" s="62"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="59"/>
       <c r="Q45" s="46"/>
-      <c r="R45" s="72"/>
-      <c r="S45" s="72"/>
+      <c r="R45" s="68"/>
+      <c r="S45" s="68"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="46"/>
       <c r="B46" s="46"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="58"/>
-      <c r="N46" s="85"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="87"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="62"/>
+      <c r="N46" s="57"/>
+      <c r="O46" s="58"/>
+      <c r="P46" s="59"/>
       <c r="Q46" s="46"/>
-      <c r="R46" s="72"/>
-      <c r="S46" s="72"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="68"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="58"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="86"/>
-      <c r="P47" s="87"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="61"/>
+      <c r="M47" s="62"/>
+      <c r="N47" s="57"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="59"/>
       <c r="Q47" s="46"/>
-      <c r="R47" s="72"/>
-      <c r="S47" s="72"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="68"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="46"/>
       <c r="B48" s="46"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="57"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="85"/>
-      <c r="O48" s="86"/>
-      <c r="P48" s="87"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="60"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
+      <c r="L48" s="61"/>
+      <c r="M48" s="62"/>
+      <c r="N48" s="57"/>
+      <c r="O48" s="58"/>
+      <c r="P48" s="59"/>
       <c r="Q48" s="46"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="72"/>
+      <c r="R48" s="68"/>
+      <c r="S48" s="68"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="46"/>
       <c r="B49" s="46"/>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="57"/>
-      <c r="L49" s="57"/>
-      <c r="M49" s="58"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="86"/>
-      <c r="P49" s="87"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
+      <c r="L49" s="61"/>
+      <c r="M49" s="62"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="59"/>
       <c r="Q49" s="46"/>
-      <c r="R49" s="72"/>
-      <c r="S49" s="72"/>
+      <c r="R49" s="68"/>
+      <c r="S49" s="68"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="46"/>
       <c r="B50" s="46"/>
-      <c r="C50" s="59"/>
-      <c r="D50" s="59"/>
-      <c r="E50" s="59"/>
-      <c r="F50" s="59"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="57"/>
-      <c r="L50" s="57"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="86"/>
-      <c r="P50" s="87"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="61"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
+      <c r="L50" s="61"/>
+      <c r="M50" s="62"/>
+      <c r="N50" s="57"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="59"/>
       <c r="Q50" s="46"/>
-      <c r="R50" s="72"/>
-      <c r="S50" s="72"/>
+      <c r="R50" s="68"/>
+      <c r="S50" s="68"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="46"/>
       <c r="B51" s="46"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
-      <c r="L51" s="57"/>
-      <c r="M51" s="58"/>
-      <c r="N51" s="85"/>
-      <c r="O51" s="86"/>
-      <c r="P51" s="87"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="60"/>
+      <c r="I51" s="61"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
+      <c r="L51" s="61"/>
+      <c r="M51" s="62"/>
+      <c r="N51" s="57"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="59"/>
       <c r="Q51" s="46"/>
-      <c r="R51" s="72"/>
-      <c r="S51" s="72"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="68"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="46"/>
       <c r="B52" s="46"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="57"/>
-      <c r="L52" s="57"/>
-      <c r="M52" s="58"/>
-      <c r="N52" s="85"/>
-      <c r="O52" s="86"/>
-      <c r="P52" s="87"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
+      <c r="L52" s="61"/>
+      <c r="M52" s="62"/>
+      <c r="N52" s="57"/>
+      <c r="O52" s="58"/>
+      <c r="P52" s="59"/>
       <c r="Q52" s="46"/>
-      <c r="R52" s="72"/>
-      <c r="S52" s="72"/>
+      <c r="R52" s="68"/>
+      <c r="S52" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="H5:M9"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C5:G9"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C47:G47"/>
     <mergeCell ref="C52:G52"/>
     <mergeCell ref="H52:M52"/>
     <mergeCell ref="C4:G4"/>
@@ -4148,16 +3969,169 @@
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H38:M38"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C5:G9"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="H5:M9"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -4221,23 +4195,23 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
-      <c r="AO1" s="107" t="s">
+      <c r="AO1" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="AP1" s="107"/>
-      <c r="AQ1" s="107"/>
-      <c r="AR1" s="107"/>
-      <c r="AS1" s="107"/>
-      <c r="AT1" s="101">
+      <c r="AP1" s="112"/>
+      <c r="AQ1" s="112"/>
+      <c r="AR1" s="112"/>
+      <c r="AS1" s="112"/>
+      <c r="AT1" s="106">
         <v>46199</v>
       </c>
-      <c r="AU1" s="102"/>
-      <c r="AV1" s="102"/>
-      <c r="AW1" s="102"/>
-      <c r="AX1" s="102"/>
-      <c r="AY1" s="102"/>
-      <c r="AZ1" s="102"/>
-      <c r="BA1" s="102"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -4283,54 +4257,54 @@
       <c r="AK4" s="8"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="103" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="104"/>
-      <c r="S5" s="105"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="110"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="106">
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="111">
         <v>1</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="104"/>
-      <c r="P6" s="104"/>
-      <c r="Q6" s="104"/>
-      <c r="R6" s="104"/>
-      <c r="S6" s="105"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="110"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -4339,61 +4313,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="98" t="s">
+      <c r="A9" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="99"/>
-      <c r="T9" s="99"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
-      <c r="AA9" s="99"/>
-      <c r="AB9" s="99"/>
-      <c r="AC9" s="99"/>
-      <c r="AD9" s="99"/>
-      <c r="AE9" s="99"/>
-      <c r="AF9" s="99"/>
-      <c r="AG9" s="99"/>
-      <c r="AH9" s="99"/>
-      <c r="AI9" s="99"/>
-      <c r="AJ9" s="99"/>
-      <c r="AK9" s="99"/>
-      <c r="AL9" s="99"/>
-      <c r="AM9" s="99"/>
-      <c r="AN9" s="99"/>
-      <c r="AO9" s="99"/>
-      <c r="AP9" s="99"/>
-      <c r="AQ9" s="99"/>
-      <c r="AR9" s="99"/>
-      <c r="AS9" s="99"/>
-      <c r="AT9" s="99"/>
-      <c r="AU9" s="99"/>
-      <c r="AV9" s="99"/>
-      <c r="AW9" s="99"/>
-      <c r="AX9" s="99"/>
-      <c r="AY9" s="99"/>
-      <c r="AZ9" s="99"/>
-      <c r="BA9" s="100"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="104"/>
+      <c r="P9" s="104"/>
+      <c r="Q9" s="104"/>
+      <c r="R9" s="104"/>
+      <c r="S9" s="104"/>
+      <c r="T9" s="104"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="104"/>
+      <c r="W9" s="104"/>
+      <c r="X9" s="104"/>
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="104"/>
+      <c r="AA9" s="104"/>
+      <c r="AB9" s="104"/>
+      <c r="AC9" s="104"/>
+      <c r="AD9" s="104"/>
+      <c r="AE9" s="104"/>
+      <c r="AF9" s="104"/>
+      <c r="AG9" s="104"/>
+      <c r="AH9" s="104"/>
+      <c r="AI9" s="104"/>
+      <c r="AJ9" s="104"/>
+      <c r="AK9" s="104"/>
+      <c r="AL9" s="104"/>
+      <c r="AM9" s="104"/>
+      <c r="AN9" s="104"/>
+      <c r="AO9" s="104"/>
+      <c r="AP9" s="104"/>
+      <c r="AQ9" s="104"/>
+      <c r="AR9" s="104"/>
+      <c r="AS9" s="104"/>
+      <c r="AT9" s="104"/>
+      <c r="AU9" s="104"/>
+      <c r="AV9" s="104"/>
+      <c r="AW9" s="104"/>
+      <c r="AX9" s="104"/>
+      <c r="AY9" s="104"/>
+      <c r="AZ9" s="104"/>
+      <c r="BA9" s="105"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="10"/>
@@ -8116,61 +8090,61 @@
       <c r="BA102" s="16"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="98" t="s">
+      <c r="A103" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="B103" s="99"/>
-      <c r="C103" s="99"/>
-      <c r="D103" s="99"/>
-      <c r="E103" s="99"/>
-      <c r="F103" s="99"/>
-      <c r="G103" s="99"/>
-      <c r="H103" s="99"/>
-      <c r="I103" s="99"/>
-      <c r="J103" s="99"/>
-      <c r="K103" s="99"/>
-      <c r="L103" s="99"/>
-      <c r="M103" s="99"/>
-      <c r="N103" s="99"/>
-      <c r="O103" s="99"/>
-      <c r="P103" s="99"/>
-      <c r="Q103" s="99"/>
-      <c r="R103" s="99"/>
-      <c r="S103" s="99"/>
-      <c r="T103" s="99"/>
-      <c r="U103" s="99"/>
-      <c r="V103" s="99"/>
-      <c r="W103" s="99"/>
-      <c r="X103" s="99"/>
-      <c r="Y103" s="99"/>
-      <c r="Z103" s="99"/>
-      <c r="AA103" s="99"/>
-      <c r="AB103" s="99"/>
-      <c r="AC103" s="99"/>
-      <c r="AD103" s="99"/>
-      <c r="AE103" s="99"/>
-      <c r="AF103" s="99"/>
-      <c r="AG103" s="99"/>
-      <c r="AH103" s="99"/>
-      <c r="AI103" s="99"/>
-      <c r="AJ103" s="99"/>
-      <c r="AK103" s="99"/>
-      <c r="AL103" s="99"/>
-      <c r="AM103" s="99"/>
-      <c r="AN103" s="99"/>
-      <c r="AO103" s="99"/>
-      <c r="AP103" s="99"/>
-      <c r="AQ103" s="99"/>
-      <c r="AR103" s="99"/>
-      <c r="AS103" s="99"/>
-      <c r="AT103" s="99"/>
-      <c r="AU103" s="99"/>
-      <c r="AV103" s="99"/>
-      <c r="AW103" s="99"/>
-      <c r="AX103" s="99"/>
-      <c r="AY103" s="99"/>
-      <c r="AZ103" s="99"/>
-      <c r="BA103" s="100"/>
+      <c r="B103" s="104"/>
+      <c r="C103" s="104"/>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="104"/>
+      <c r="G103" s="104"/>
+      <c r="H103" s="104"/>
+      <c r="I103" s="104"/>
+      <c r="J103" s="104"/>
+      <c r="K103" s="104"/>
+      <c r="L103" s="104"/>
+      <c r="M103" s="104"/>
+      <c r="N103" s="104"/>
+      <c r="O103" s="104"/>
+      <c r="P103" s="104"/>
+      <c r="Q103" s="104"/>
+      <c r="R103" s="104"/>
+      <c r="S103" s="104"/>
+      <c r="T103" s="104"/>
+      <c r="U103" s="104"/>
+      <c r="V103" s="104"/>
+      <c r="W103" s="104"/>
+      <c r="X103" s="104"/>
+      <c r="Y103" s="104"/>
+      <c r="Z103" s="104"/>
+      <c r="AA103" s="104"/>
+      <c r="AB103" s="104"/>
+      <c r="AC103" s="104"/>
+      <c r="AD103" s="104"/>
+      <c r="AE103" s="104"/>
+      <c r="AF103" s="104"/>
+      <c r="AG103" s="104"/>
+      <c r="AH103" s="104"/>
+      <c r="AI103" s="104"/>
+      <c r="AJ103" s="104"/>
+      <c r="AK103" s="104"/>
+      <c r="AL103" s="104"/>
+      <c r="AM103" s="104"/>
+      <c r="AN103" s="104"/>
+      <c r="AO103" s="104"/>
+      <c r="AP103" s="104"/>
+      <c r="AQ103" s="104"/>
+      <c r="AR103" s="104"/>
+      <c r="AS103" s="104"/>
+      <c r="AT103" s="104"/>
+      <c r="AU103" s="104"/>
+      <c r="AV103" s="104"/>
+      <c r="AW103" s="104"/>
+      <c r="AX103" s="104"/>
+      <c r="AY103" s="104"/>
+      <c r="AZ103" s="104"/>
+      <c r="BA103" s="105"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="12"/>
@@ -8493,61 +8467,61 @@
       <c r="BA111" s="16"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="98" t="s">
+      <c r="A112" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="B112" s="99"/>
-      <c r="C112" s="99"/>
-      <c r="D112" s="99"/>
-      <c r="E112" s="99"/>
-      <c r="F112" s="99"/>
-      <c r="G112" s="99"/>
-      <c r="H112" s="99"/>
-      <c r="I112" s="99"/>
-      <c r="J112" s="99"/>
-      <c r="K112" s="99"/>
-      <c r="L112" s="99"/>
-      <c r="M112" s="99"/>
-      <c r="N112" s="99"/>
-      <c r="O112" s="99"/>
-      <c r="P112" s="99"/>
-      <c r="Q112" s="99"/>
-      <c r="R112" s="99"/>
-      <c r="S112" s="99"/>
-      <c r="T112" s="99"/>
-      <c r="U112" s="99"/>
-      <c r="V112" s="99"/>
-      <c r="W112" s="99"/>
-      <c r="X112" s="99"/>
-      <c r="Y112" s="99"/>
-      <c r="Z112" s="99"/>
-      <c r="AA112" s="99"/>
-      <c r="AB112" s="99"/>
-      <c r="AC112" s="99"/>
-      <c r="AD112" s="99"/>
-      <c r="AE112" s="99"/>
-      <c r="AF112" s="99"/>
-      <c r="AG112" s="99"/>
-      <c r="AH112" s="99"/>
-      <c r="AI112" s="99"/>
-      <c r="AJ112" s="99"/>
-      <c r="AK112" s="99"/>
-      <c r="AL112" s="99"/>
-      <c r="AM112" s="99"/>
-      <c r="AN112" s="99"/>
-      <c r="AO112" s="99"/>
-      <c r="AP112" s="99"/>
-      <c r="AQ112" s="99"/>
-      <c r="AR112" s="99"/>
-      <c r="AS112" s="99"/>
-      <c r="AT112" s="99"/>
-      <c r="AU112" s="99"/>
-      <c r="AV112" s="99"/>
-      <c r="AW112" s="99"/>
-      <c r="AX112" s="99"/>
-      <c r="AY112" s="99"/>
-      <c r="AZ112" s="99"/>
-      <c r="BA112" s="99"/>
+      <c r="B112" s="104"/>
+      <c r="C112" s="104"/>
+      <c r="D112" s="104"/>
+      <c r="E112" s="104"/>
+      <c r="F112" s="104"/>
+      <c r="G112" s="104"/>
+      <c r="H112" s="104"/>
+      <c r="I112" s="104"/>
+      <c r="J112" s="104"/>
+      <c r="K112" s="104"/>
+      <c r="L112" s="104"/>
+      <c r="M112" s="104"/>
+      <c r="N112" s="104"/>
+      <c r="O112" s="104"/>
+      <c r="P112" s="104"/>
+      <c r="Q112" s="104"/>
+      <c r="R112" s="104"/>
+      <c r="S112" s="104"/>
+      <c r="T112" s="104"/>
+      <c r="U112" s="104"/>
+      <c r="V112" s="104"/>
+      <c r="W112" s="104"/>
+      <c r="X112" s="104"/>
+      <c r="Y112" s="104"/>
+      <c r="Z112" s="104"/>
+      <c r="AA112" s="104"/>
+      <c r="AB112" s="104"/>
+      <c r="AC112" s="104"/>
+      <c r="AD112" s="104"/>
+      <c r="AE112" s="104"/>
+      <c r="AF112" s="104"/>
+      <c r="AG112" s="104"/>
+      <c r="AH112" s="104"/>
+      <c r="AI112" s="104"/>
+      <c r="AJ112" s="104"/>
+      <c r="AK112" s="104"/>
+      <c r="AL112" s="104"/>
+      <c r="AM112" s="104"/>
+      <c r="AN112" s="104"/>
+      <c r="AO112" s="104"/>
+      <c r="AP112" s="104"/>
+      <c r="AQ112" s="104"/>
+      <c r="AR112" s="104"/>
+      <c r="AS112" s="104"/>
+      <c r="AT112" s="104"/>
+      <c r="AU112" s="104"/>
+      <c r="AV112" s="104"/>
+      <c r="AW112" s="104"/>
+      <c r="AX112" s="104"/>
+      <c r="AY112" s="104"/>
+      <c r="AZ112" s="104"/>
+      <c r="BA112" s="104"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="12"/>
@@ -8734,178 +8708,178 @@
       <c r="G1" s="147" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="133"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="132"/>
       <c r="K1" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="133"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="132"/>
       <c r="O1" s="147" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="133"/>
+      <c r="P1" s="132"/>
       <c r="Q1" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="R1" s="133"/>
+      <c r="R1" s="132"/>
       <c r="S1" s="147" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="135"/>
+      <c r="T1" s="134"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="145"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="122" t="s">
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="122" t="s">
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="124"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="123"/>
       <c r="O2" s="138">
         <v>46199</v>
       </c>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="122" t="s">
+      <c r="P2" s="123"/>
+      <c r="Q2" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="124"/>
-      <c r="S2" s="122"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="121"/>
       <c r="T2" s="139"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="145"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="125"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="125"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="126"/>
+      <c r="S3" s="124"/>
       <c r="T3" s="140"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="146"/>
-      <c r="B4" s="129"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="129"/>
-      <c r="M4" s="129"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="130"/>
-      <c r="S4" s="128"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="127"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="127"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="127"/>
       <c r="T4" s="141"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="132"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="134" t="s">
+      <c r="B5" s="131"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="132"/>
-      <c r="P5" s="132"/>
-      <c r="Q5" s="132"/>
-      <c r="R5" s="132"/>
-      <c r="S5" s="132"/>
-      <c r="T5" s="135"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="131"/>
+      <c r="K5" s="131"/>
+      <c r="L5" s="131"/>
+      <c r="M5" s="131"/>
+      <c r="N5" s="131"/>
+      <c r="O5" s="131"/>
+      <c r="P5" s="131"/>
+      <c r="Q5" s="131"/>
+      <c r="R5" s="131"/>
+      <c r="S5" s="131"/>
+      <c r="T5" s="134"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="109"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
       <c r="G6" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115"/>
-      <c r="N6" s="115"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="115"/>
-      <c r="S6" s="115"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="117"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="117"/>
+      <c r="S6" s="117"/>
       <c r="T6" s="137"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="119" t="s">
+      <c r="A7" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="115"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="109"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="115"/>
-      <c r="N7" s="115"/>
-      <c r="O7" s="115"/>
-      <c r="P7" s="115"/>
-      <c r="Q7" s="115"/>
-      <c r="R7" s="115"/>
-      <c r="S7" s="115"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+      <c r="N7" s="117"/>
+      <c r="O7" s="117"/>
+      <c r="P7" s="117"/>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="117"/>
       <c r="T7" s="137"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
@@ -9105,37 +9079,37 @@
       <c r="T14" s="30"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="119" t="s">
+      <c r="A15" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="109"/>
-      <c r="C15" s="121" t="s">
+      <c r="B15" s="118"/>
+      <c r="C15" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="109"/>
-      <c r="E15" s="118" t="s">
+      <c r="D15" s="118"/>
+      <c r="E15" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="109"/>
-      <c r="G15" s="118" t="s">
+      <c r="F15" s="118"/>
+      <c r="G15" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="115"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="118" t="s">
+      <c r="H15" s="117"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="109"/>
-      <c r="L15" s="118" t="s">
+      <c r="K15" s="118"/>
+      <c r="L15" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="115"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="118" t="s">
+      <c r="M15" s="117"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="115"/>
-      <c r="Q15" s="109"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="118"/>
       <c r="R15" s="29" t="s">
         <v>36</v>
       </c>
@@ -9147,37 +9121,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="110">
+      <c r="A16" s="149">
         <v>1</v>
       </c>
-      <c r="B16" s="109"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="109"/>
-      <c r="E16" s="108" t="s">
+      <c r="D16" s="118"/>
+      <c r="E16" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="109"/>
-      <c r="G16" s="120" t="s">
+      <c r="F16" s="118"/>
+      <c r="G16" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="115"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="120" t="s">
+      <c r="H16" s="117"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="109"/>
-      <c r="L16" s="114" t="s">
+      <c r="K16" s="118"/>
+      <c r="L16" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="115"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="114" t="s">
+      <c r="M16" s="117"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="109"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="118"/>
       <c r="R16" s="27">
         <v>46199</v>
       </c>
@@ -9195,37 +9169,37 @@
       <c r="Z16" s="20"/>
     </row>
     <row r="17" spans="1:26" ht="66.75" customHeight="1">
-      <c r="A17" s="110">
+      <c r="A17" s="149">
         <v>2</v>
       </c>
-      <c r="B17" s="109"/>
-      <c r="C17" s="108" t="s">
+      <c r="B17" s="118"/>
+      <c r="C17" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="109"/>
-      <c r="E17" s="108" t="s">
+      <c r="D17" s="118"/>
+      <c r="E17" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="109"/>
-      <c r="G17" s="149" t="s">
+      <c r="F17" s="118"/>
+      <c r="G17" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="150"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="120" t="s">
+      <c r="H17" s="153"/>
+      <c r="I17" s="154"/>
+      <c r="J17" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="109"/>
-      <c r="L17" s="114" t="s">
+      <c r="K17" s="118"/>
+      <c r="L17" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="115"/>
-      <c r="N17" s="109"/>
-      <c r="O17" s="114" t="s">
+      <c r="M17" s="117"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="P17" s="115"/>
-      <c r="Q17" s="109"/>
+      <c r="P17" s="117"/>
+      <c r="Q17" s="118"/>
       <c r="R17" s="27">
         <v>46199</v>
       </c>
@@ -9243,37 +9217,37 @@
       <c r="Z17" s="20"/>
     </row>
     <row r="18" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A18" s="110">
+      <c r="A18" s="149">
         <v>3</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="108" t="s">
+      <c r="B18" s="118"/>
+      <c r="C18" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="109"/>
-      <c r="E18" s="108" t="s">
+      <c r="D18" s="118"/>
+      <c r="E18" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="109"/>
-      <c r="G18" s="120" t="s">
+      <c r="F18" s="118"/>
+      <c r="G18" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="115"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="120" t="s">
+      <c r="H18" s="117"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="109"/>
-      <c r="L18" s="114" t="s">
+      <c r="K18" s="118"/>
+      <c r="L18" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="115"/>
-      <c r="N18" s="109"/>
-      <c r="O18" s="114" t="s">
+      <c r="M18" s="117"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="109"/>
+      <c r="P18" s="117"/>
+      <c r="Q18" s="118"/>
       <c r="R18" s="27">
         <v>46199</v>
       </c>
@@ -9291,37 +9265,37 @@
       <c r="Z18" s="20"/>
     </row>
     <row r="19" spans="1:26" ht="51.75" customHeight="1">
-      <c r="A19" s="110">
+      <c r="A19" s="149">
         <v>4</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="108" t="s">
+      <c r="B19" s="118"/>
+      <c r="C19" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="109"/>
-      <c r="E19" s="108" t="s">
+      <c r="D19" s="118"/>
+      <c r="E19" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="109"/>
-      <c r="G19" s="120" t="s">
+      <c r="F19" s="118"/>
+      <c r="G19" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="115"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="120" t="s">
+      <c r="H19" s="117"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="109"/>
-      <c r="L19" s="114" t="s">
+      <c r="K19" s="118"/>
+      <c r="L19" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="M19" s="115"/>
-      <c r="N19" s="109"/>
-      <c r="O19" s="114" t="s">
+      <c r="M19" s="117"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="P19" s="115"/>
-      <c r="Q19" s="109"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="118"/>
       <c r="R19" s="27">
         <v>46199</v>
       </c>
@@ -9339,37 +9313,37 @@
       <c r="Z19" s="20"/>
     </row>
     <row r="20" spans="1:26" ht="35.25" customHeight="1">
-      <c r="A20" s="110">
+      <c r="A20" s="149">
         <v>5</v>
       </c>
-      <c r="B20" s="109"/>
-      <c r="C20" s="108" t="s">
+      <c r="B20" s="118"/>
+      <c r="C20" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="109"/>
-      <c r="E20" s="108" t="s">
+      <c r="D20" s="118"/>
+      <c r="E20" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="109"/>
-      <c r="G20" s="120" t="s">
+      <c r="F20" s="118"/>
+      <c r="G20" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="115"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="120" t="s">
+      <c r="H20" s="117"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="K20" s="109"/>
-      <c r="L20" s="114" t="s">
+      <c r="K20" s="118"/>
+      <c r="L20" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="M20" s="115"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="114" t="s">
+      <c r="M20" s="117"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="P20" s="115"/>
-      <c r="Q20" s="109"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="118"/>
       <c r="R20" s="27">
         <v>46199</v>
       </c>
@@ -9387,23 +9361,23 @@
       <c r="Z20" s="20"/>
     </row>
     <row r="21" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A21" s="110"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="109"/>
+      <c r="A21" s="149"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="118"/>
       <c r="R21" s="24"/>
       <c r="S21" s="24"/>
       <c r="T21" s="23"/>
@@ -9415,23 +9389,23 @@
       <c r="Z21" s="20"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="110"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="109"/>
+      <c r="A22" s="149"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="117"/>
+      <c r="Q22" s="118"/>
       <c r="R22" s="24"/>
       <c r="S22" s="24"/>
       <c r="T22" s="23"/>
@@ -9443,23 +9417,23 @@
       <c r="Z22" s="20"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="110"/>
-      <c r="B23" s="109"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="109"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="109"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="115"/>
-      <c r="Q23" s="109"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="150"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="117"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="118"/>
       <c r="R23" s="24"/>
       <c r="S23" s="24"/>
       <c r="T23" s="23"/>
@@ -9471,23 +9445,23 @@
       <c r="Z23" s="20"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="110"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="115"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="120"/>
-      <c r="K24" s="109"/>
-      <c r="L24" s="114"/>
-      <c r="M24" s="115"/>
-      <c r="N24" s="109"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="115"/>
-      <c r="Q24" s="109"/>
+      <c r="A24" s="149"/>
+      <c r="B24" s="118"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="117"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="117"/>
+      <c r="Q24" s="118"/>
       <c r="R24" s="24"/>
       <c r="S24" s="24"/>
       <c r="T24" s="23"/>
@@ -9499,23 +9473,23 @@
       <c r="Z24" s="20"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="109"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="109"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="115"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="109"/>
+      <c r="A25" s="149"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="118"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="118"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="117"/>
+      <c r="N25" s="118"/>
+      <c r="O25" s="119"/>
+      <c r="P25" s="117"/>
+      <c r="Q25" s="118"/>
       <c r="R25" s="24"/>
       <c r="S25" s="24"/>
       <c r="T25" s="23"/>
@@ -9527,23 +9501,23 @@
       <c r="Z25" s="20"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="109"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="109"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="109"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="115"/>
-      <c r="N26" s="109"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="115"/>
-      <c r="Q26" s="109"/>
+      <c r="A26" s="149"/>
+      <c r="B26" s="118"/>
+      <c r="C26" s="150"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="118"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="118"/>
       <c r="R26" s="24"/>
       <c r="S26" s="24"/>
       <c r="T26" s="23"/>
@@ -9555,23 +9529,23 @@
       <c r="Z26" s="20"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="110"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="109"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="109"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="115"/>
-      <c r="N27" s="109"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="115"/>
-      <c r="Q27" s="109"/>
+      <c r="A27" s="149"/>
+      <c r="B27" s="118"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="117"/>
+      <c r="N27" s="118"/>
+      <c r="O27" s="119"/>
+      <c r="P27" s="117"/>
+      <c r="Q27" s="118"/>
       <c r="R27" s="24"/>
       <c r="S27" s="24"/>
       <c r="T27" s="23"/>
@@ -9583,23 +9557,23 @@
       <c r="Z27" s="20"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="110"/>
-      <c r="B28" s="109"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="109"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="109"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="115"/>
-      <c r="N28" s="109"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="115"/>
-      <c r="Q28" s="109"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="118"/>
+      <c r="C28" s="150"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="150"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="117"/>
+      <c r="Q28" s="118"/>
       <c r="R28" s="24"/>
       <c r="S28" s="24"/>
       <c r="T28" s="23"/>
@@ -9611,23 +9585,23 @@
       <c r="Z28" s="20"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="110"/>
-      <c r="B29" s="109"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="109"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="109"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="109"/>
-      <c r="L29" s="114"/>
-      <c r="M29" s="115"/>
-      <c r="N29" s="109"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="115"/>
-      <c r="Q29" s="109"/>
+      <c r="A29" s="149"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="150"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="117"/>
+      <c r="I29" s="118"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="118"/>
+      <c r="L29" s="119"/>
+      <c r="M29" s="117"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="117"/>
+      <c r="Q29" s="118"/>
       <c r="R29" s="24"/>
       <c r="S29" s="24"/>
       <c r="T29" s="23"/>
@@ -9639,23 +9613,23 @@
       <c r="Z29" s="20"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="110"/>
-      <c r="B30" s="109"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="109"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="109"/>
-      <c r="L30" s="114"/>
-      <c r="M30" s="115"/>
-      <c r="N30" s="109"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="115"/>
-      <c r="Q30" s="109"/>
+      <c r="A30" s="149"/>
+      <c r="B30" s="118"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="116"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="117"/>
+      <c r="Q30" s="118"/>
       <c r="R30" s="24"/>
       <c r="S30" s="24"/>
       <c r="T30" s="23"/>
@@ -9667,23 +9641,23 @@
       <c r="Z30" s="20"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A31" s="111"/>
-      <c r="B31" s="112"/>
-      <c r="C31" s="113"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="148"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="117"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="116"/>
-      <c r="P31" s="117"/>
-      <c r="Q31" s="112"/>
+      <c r="A31" s="155"/>
+      <c r="B31" s="115"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="114"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="114"/>
+      <c r="N31" s="115"/>
+      <c r="O31" s="120"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="115"/>
       <c r="R31" s="22"/>
       <c r="S31" s="22"/>
       <c r="T31" s="21"/>
@@ -10681,56 +10655,68 @@
     <row r="1000" s="18" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="O16:Q16"/>
@@ -10754,69 +10740,57 @@
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="G16:I16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10879,23 +10853,23 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
-      <c r="AO1" s="107" t="s">
+      <c r="AO1" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="AP1" s="107"/>
-      <c r="AQ1" s="107"/>
-      <c r="AR1" s="107"/>
-      <c r="AS1" s="107"/>
-      <c r="AT1" s="101">
+      <c r="AP1" s="112"/>
+      <c r="AQ1" s="112"/>
+      <c r="AR1" s="112"/>
+      <c r="AS1" s="112"/>
+      <c r="AT1" s="106">
         <v>44861</v>
       </c>
-      <c r="AU1" s="102"/>
-      <c r="AV1" s="102"/>
-      <c r="AW1" s="102"/>
-      <c r="AX1" s="102"/>
-      <c r="AY1" s="102"/>
-      <c r="AZ1" s="102"/>
-      <c r="BA1" s="102"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -10941,54 +10915,54 @@
       <c r="AK4" s="8"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="103" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="104"/>
-      <c r="S5" s="105"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="110"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="106">
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="111">
         <v>1</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="104"/>
-      <c r="P6" s="104"/>
-      <c r="Q6" s="104"/>
-      <c r="R6" s="104"/>
-      <c r="S6" s="105"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="110"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -10997,61 +10971,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="98" t="s">
+      <c r="A9" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="99"/>
-      <c r="T9" s="99"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
-      <c r="AA9" s="99"/>
-      <c r="AB9" s="99"/>
-      <c r="AC9" s="99"/>
-      <c r="AD9" s="99"/>
-      <c r="AE9" s="99"/>
-      <c r="AF9" s="99"/>
-      <c r="AG9" s="99"/>
-      <c r="AH9" s="99"/>
-      <c r="AI9" s="99"/>
-      <c r="AJ9" s="99"/>
-      <c r="AK9" s="99"/>
-      <c r="AL9" s="99"/>
-      <c r="AM9" s="99"/>
-      <c r="AN9" s="99"/>
-      <c r="AO9" s="99"/>
-      <c r="AP9" s="99"/>
-      <c r="AQ9" s="99"/>
-      <c r="AR9" s="99"/>
-      <c r="AS9" s="99"/>
-      <c r="AT9" s="99"/>
-      <c r="AU9" s="99"/>
-      <c r="AV9" s="99"/>
-      <c r="AW9" s="99"/>
-      <c r="AX9" s="99"/>
-      <c r="AY9" s="99"/>
-      <c r="AZ9" s="99"/>
-      <c r="BA9" s="100"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="104"/>
+      <c r="P9" s="104"/>
+      <c r="Q9" s="104"/>
+      <c r="R9" s="104"/>
+      <c r="S9" s="104"/>
+      <c r="T9" s="104"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="104"/>
+      <c r="W9" s="104"/>
+      <c r="X9" s="104"/>
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="104"/>
+      <c r="AA9" s="104"/>
+      <c r="AB9" s="104"/>
+      <c r="AC9" s="104"/>
+      <c r="AD9" s="104"/>
+      <c r="AE9" s="104"/>
+      <c r="AF9" s="104"/>
+      <c r="AG9" s="104"/>
+      <c r="AH9" s="104"/>
+      <c r="AI9" s="104"/>
+      <c r="AJ9" s="104"/>
+      <c r="AK9" s="104"/>
+      <c r="AL9" s="104"/>
+      <c r="AM9" s="104"/>
+      <c r="AN9" s="104"/>
+      <c r="AO9" s="104"/>
+      <c r="AP9" s="104"/>
+      <c r="AQ9" s="104"/>
+      <c r="AR9" s="104"/>
+      <c r="AS9" s="104"/>
+      <c r="AT9" s="104"/>
+      <c r="AU9" s="104"/>
+      <c r="AV9" s="104"/>
+      <c r="AW9" s="104"/>
+      <c r="AX9" s="104"/>
+      <c r="AY9" s="104"/>
+      <c r="AZ9" s="104"/>
+      <c r="BA9" s="105"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="10"/>
@@ -12014,61 +11988,61 @@
       <c r="BA33" s="16"/>
     </row>
     <row r="34" spans="1:53" ht="18" customHeight="1">
-      <c r="A34" s="98" t="s">
+      <c r="A34" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="99"/>
-      <c r="C34" s="99"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="99"/>
-      <c r="I34" s="99"/>
-      <c r="J34" s="99"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="99"/>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="99"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="99"/>
-      <c r="R34" s="99"/>
-      <c r="S34" s="99"/>
-      <c r="T34" s="99"/>
-      <c r="U34" s="99"/>
-      <c r="V34" s="99"/>
-      <c r="W34" s="99"/>
-      <c r="X34" s="99"/>
-      <c r="Y34" s="99"/>
-      <c r="Z34" s="99"/>
-      <c r="AA34" s="99"/>
-      <c r="AB34" s="99"/>
-      <c r="AC34" s="99"/>
-      <c r="AD34" s="99"/>
-      <c r="AE34" s="99"/>
-      <c r="AF34" s="99"/>
-      <c r="AG34" s="99"/>
-      <c r="AH34" s="99"/>
-      <c r="AI34" s="99"/>
-      <c r="AJ34" s="99"/>
-      <c r="AK34" s="99"/>
-      <c r="AL34" s="99"/>
-      <c r="AM34" s="99"/>
-      <c r="AN34" s="99"/>
-      <c r="AO34" s="99"/>
-      <c r="AP34" s="99"/>
-      <c r="AQ34" s="99"/>
-      <c r="AR34" s="99"/>
-      <c r="AS34" s="99"/>
-      <c r="AT34" s="99"/>
-      <c r="AU34" s="99"/>
-      <c r="AV34" s="99"/>
-      <c r="AW34" s="99"/>
-      <c r="AX34" s="99"/>
-      <c r="AY34" s="99"/>
-      <c r="AZ34" s="99"/>
-      <c r="BA34" s="100"/>
+      <c r="B34" s="104"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="104"/>
+      <c r="N34" s="104"/>
+      <c r="O34" s="104"/>
+      <c r="P34" s="104"/>
+      <c r="Q34" s="104"/>
+      <c r="R34" s="104"/>
+      <c r="S34" s="104"/>
+      <c r="T34" s="104"/>
+      <c r="U34" s="104"/>
+      <c r="V34" s="104"/>
+      <c r="W34" s="104"/>
+      <c r="X34" s="104"/>
+      <c r="Y34" s="104"/>
+      <c r="Z34" s="104"/>
+      <c r="AA34" s="104"/>
+      <c r="AB34" s="104"/>
+      <c r="AC34" s="104"/>
+      <c r="AD34" s="104"/>
+      <c r="AE34" s="104"/>
+      <c r="AF34" s="104"/>
+      <c r="AG34" s="104"/>
+      <c r="AH34" s="104"/>
+      <c r="AI34" s="104"/>
+      <c r="AJ34" s="104"/>
+      <c r="AK34" s="104"/>
+      <c r="AL34" s="104"/>
+      <c r="AM34" s="104"/>
+      <c r="AN34" s="104"/>
+      <c r="AO34" s="104"/>
+      <c r="AP34" s="104"/>
+      <c r="AQ34" s="104"/>
+      <c r="AR34" s="104"/>
+      <c r="AS34" s="104"/>
+      <c r="AT34" s="104"/>
+      <c r="AU34" s="104"/>
+      <c r="AV34" s="104"/>
+      <c r="AW34" s="104"/>
+      <c r="AX34" s="104"/>
+      <c r="AY34" s="104"/>
+      <c r="AZ34" s="104"/>
+      <c r="BA34" s="105"/>
     </row>
     <row r="35" spans="1:53" ht="21.95" customHeight="1">
       <c r="A35" s="12"/>
@@ -12391,61 +12365,61 @@
       <c r="BA42" s="16"/>
     </row>
     <row r="43" spans="1:53" ht="18" customHeight="1">
-      <c r="A43" s="98" t="s">
+      <c r="A43" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="99"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
-      <c r="S43" s="99"/>
-      <c r="T43" s="99"/>
-      <c r="U43" s="99"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="99"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="99"/>
-      <c r="AB43" s="99"/>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="99"/>
-      <c r="AE43" s="99"/>
-      <c r="AF43" s="99"/>
-      <c r="AG43" s="99"/>
-      <c r="AH43" s="99"/>
-      <c r="AI43" s="99"/>
-      <c r="AJ43" s="99"/>
-      <c r="AK43" s="99"/>
-      <c r="AL43" s="99"/>
-      <c r="AM43" s="99"/>
-      <c r="AN43" s="99"/>
-      <c r="AO43" s="99"/>
-      <c r="AP43" s="99"/>
-      <c r="AQ43" s="99"/>
-      <c r="AR43" s="99"/>
-      <c r="AS43" s="99"/>
-      <c r="AT43" s="99"/>
-      <c r="AU43" s="99"/>
-      <c r="AV43" s="99"/>
-      <c r="AW43" s="99"/>
-      <c r="AX43" s="99"/>
-      <c r="AY43" s="99"/>
-      <c r="AZ43" s="99"/>
-      <c r="BA43" s="99"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="104"/>
+      <c r="P43" s="104"/>
+      <c r="Q43" s="104"/>
+      <c r="R43" s="104"/>
+      <c r="S43" s="104"/>
+      <c r="T43" s="104"/>
+      <c r="U43" s="104"/>
+      <c r="V43" s="104"/>
+      <c r="W43" s="104"/>
+      <c r="X43" s="104"/>
+      <c r="Y43" s="104"/>
+      <c r="Z43" s="104"/>
+      <c r="AA43" s="104"/>
+      <c r="AB43" s="104"/>
+      <c r="AC43" s="104"/>
+      <c r="AD43" s="104"/>
+      <c r="AE43" s="104"/>
+      <c r="AF43" s="104"/>
+      <c r="AG43" s="104"/>
+      <c r="AH43" s="104"/>
+      <c r="AI43" s="104"/>
+      <c r="AJ43" s="104"/>
+      <c r="AK43" s="104"/>
+      <c r="AL43" s="104"/>
+      <c r="AM43" s="104"/>
+      <c r="AN43" s="104"/>
+      <c r="AO43" s="104"/>
+      <c r="AP43" s="104"/>
+      <c r="AQ43" s="104"/>
+      <c r="AR43" s="104"/>
+      <c r="AS43" s="104"/>
+      <c r="AT43" s="104"/>
+      <c r="AU43" s="104"/>
+      <c r="AV43" s="104"/>
+      <c r="AW43" s="104"/>
+      <c r="AX43" s="104"/>
+      <c r="AY43" s="104"/>
+      <c r="AZ43" s="104"/>
+      <c r="BA43" s="104"/>
     </row>
     <row r="44" spans="1:53" ht="21.95" customHeight="1">
       <c r="A44" s="12"/>
@@ -12622,70 +12596,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="85" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="79"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="64"/>
       <c r="N1" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="O1" s="77" t="s">
+      <c r="O1" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="79"/>
+      <c r="P1" s="64"/>
       <c r="Q1" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="R1" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="S1" s="79"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="64"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="74" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="75"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="77" t="s">
+      <c r="D2" s="87"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="79"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="64"/>
       <c r="N2" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="94">
+      <c r="O2" s="65">
         <v>46202</v>
       </c>
-      <c r="P2" s="95"/>
+      <c r="P2" s="66"/>
       <c r="Q2" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="R2" s="156"/>
-      <c r="S2" s="97"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="82"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="53"/>
@@ -12715,54 +12687,54 @@
       <c r="B4" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="60" t="s">
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="60" t="s">
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="61"/>
-      <c r="P4" s="62"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="71"/>
       <c r="Q4" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="R4" s="60" t="s">
+      <c r="R4" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="S4" s="62"/>
+      <c r="S4" s="71"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="49"/>
-      <c r="B5" s="155"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
-      <c r="L5" s="154"/>
-      <c r="M5" s="154"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="89"/>
-      <c r="P5" s="90"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="74"/>
       <c r="Q5" s="49"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="84"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="46">
@@ -12771,208 +12743,208 @@
       <c r="B6" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59" t="s">
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="91" t="s">
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="O6" s="92"/>
-      <c r="P6" s="93"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="76"/>
       <c r="Q6" s="47">
         <v>46202</v>
       </c>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="46"/>
       <c r="B7" s="46"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="87"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="59"/>
       <c r="Q7" s="47"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" spans="1:19" ht="42.75" customHeight="1">
       <c r="A8" s="46"/>
       <c r="B8" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="59" t="s">
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="83" t="s">
         <v>110</v>
       </c>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="91" t="s">
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="O8" s="86"/>
-      <c r="P8" s="87"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="59"/>
       <c r="Q8" s="47">
         <v>46202</v>
       </c>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="59"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="86"/>
-      <c r="P9" s="87"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="59"/>
       <c r="Q9" s="47"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="68"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="46"/>
       <c r="B10" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="56" t="s">
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="91" t="s">
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="O10" s="86"/>
-      <c r="P10" s="87"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="59"/>
       <c r="Q10" s="47">
         <v>46202</v>
       </c>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
+      <c r="R10" s="68"/>
+      <c r="S10" s="68"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="46"/>
       <c r="B11" s="46"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="86"/>
-      <c r="P11" s="87"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="59"/>
       <c r="Q11" s="47"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="56" t="s">
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="91" t="s">
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="O12" s="86"/>
-      <c r="P12" s="87"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="59"/>
       <c r="Q12" s="47">
         <v>46202</v>
       </c>
-      <c r="R12" s="63"/>
-      <c r="S12" s="65"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="78"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="46"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="87"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="59"/>
       <c r="Q13" s="47"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="68"/>
     </row>
     <row r="14" spans="1:19" ht="37.5" customHeight="1">
       <c r="A14" s="46">
@@ -12981,52 +12953,52 @@
       <c r="B14" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="153" t="s">
+      <c r="C14" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="56" t="s">
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="85" t="s">
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="O14" s="86"/>
-      <c r="P14" s="87"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="59"/>
       <c r="Q14" s="47">
         <v>46202</v>
       </c>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="46"/>
       <c r="B15" s="46"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="87"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="59"/>
       <c r="Q15" s="47"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="68"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="46">
@@ -13035,52 +13007,52 @@
       <c r="B16" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="56" t="s">
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="91" t="s">
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="O16" s="86"/>
-      <c r="P16" s="87"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="59"/>
       <c r="Q16" s="47">
         <v>46202</v>
       </c>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
+      <c r="R16" s="68"/>
+      <c r="S16" s="68"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="46"/>
       <c r="B17" s="46"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="86"/>
-      <c r="P17" s="87"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="59"/>
       <c r="Q17" s="47"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="68"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="46">
@@ -13089,698 +13061,783 @@
       <c r="B18" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="56" t="s">
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="85" t="s">
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="O18" s="86"/>
-      <c r="P18" s="87"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="59"/>
       <c r="Q18" s="47">
         <v>46202</v>
       </c>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="46"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="86"/>
-      <c r="P19" s="87"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="59"/>
       <c r="Q19" s="46"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="46"/>
       <c r="B20" s="46"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="86"/>
-      <c r="P20" s="87"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="59"/>
       <c r="Q20" s="46"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="46"/>
       <c r="B21" s="46"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="86"/>
-      <c r="P21" s="87"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="59"/>
       <c r="Q21" s="46"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="46"/>
       <c r="B22" s="46"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="87"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="59"/>
       <c r="Q22" s="46"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="68"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="86"/>
-      <c r="P23" s="87"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="59"/>
       <c r="Q23" s="46"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="46"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="87"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="59"/>
       <c r="Q24" s="46"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
+      <c r="R24" s="68"/>
+      <c r="S24" s="68"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="46"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="87"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="59"/>
       <c r="Q25" s="46"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="68"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="86"/>
-      <c r="P26" s="87"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="59"/>
       <c r="Q26" s="46"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="72"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="46"/>
       <c r="B27" s="46"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="86"/>
-      <c r="P27" s="87"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="59"/>
       <c r="Q27" s="46"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="72"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="68"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="46"/>
       <c r="B28" s="46"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="87"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="59"/>
       <c r="Q28" s="46"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="46"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="87"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="59"/>
       <c r="Q29" s="46"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="72"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="46"/>
       <c r="B30" s="46"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="87"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="59"/>
       <c r="Q30" s="46"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="72"/>
+      <c r="R30" s="68"/>
+      <c r="S30" s="68"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="86"/>
-      <c r="P31" s="87"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="59"/>
       <c r="Q31" s="46"/>
-      <c r="R31" s="72"/>
-      <c r="S31" s="72"/>
+      <c r="R31" s="68"/>
+      <c r="S31" s="68"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="86"/>
-      <c r="P32" s="87"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="59"/>
       <c r="Q32" s="46"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="72"/>
+      <c r="R32" s="68"/>
+      <c r="S32" s="68"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="46"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="87"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="59"/>
       <c r="Q33" s="46"/>
-      <c r="R33" s="72"/>
-      <c r="S33" s="72"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="68"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="46"/>
       <c r="B34" s="46"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="58"/>
-      <c r="N34" s="85"/>
-      <c r="O34" s="86"/>
-      <c r="P34" s="87"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="59"/>
       <c r="Q34" s="46"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="72"/>
+      <c r="R34" s="68"/>
+      <c r="S34" s="68"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="85"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="87"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="83"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="57"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="59"/>
       <c r="Q35" s="46"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
+      <c r="R35" s="68"/>
+      <c r="S35" s="68"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="86"/>
-      <c r="P36" s="87"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="59"/>
       <c r="Q36" s="46"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="68"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="46"/>
       <c r="B37" s="46"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="58"/>
-      <c r="N37" s="85"/>
-      <c r="O37" s="86"/>
-      <c r="P37" s="87"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="59"/>
       <c r="Q37" s="46"/>
-      <c r="R37" s="72"/>
-      <c r="S37" s="72"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="68"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="85"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="87"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="59"/>
       <c r="Q38" s="46"/>
-      <c r="R38" s="72"/>
-      <c r="S38" s="72"/>
+      <c r="R38" s="68"/>
+      <c r="S38" s="68"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="58"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="86"/>
-      <c r="P39" s="87"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="59"/>
       <c r="Q39" s="46"/>
-      <c r="R39" s="72"/>
-      <c r="S39" s="72"/>
+      <c r="R39" s="68"/>
+      <c r="S39" s="68"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="46"/>
       <c r="B40" s="46"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="85"/>
-      <c r="O40" s="86"/>
-      <c r="P40" s="87"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="62"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="59"/>
       <c r="Q40" s="46"/>
-      <c r="R40" s="72"/>
-      <c r="S40" s="72"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="68"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="85"/>
-      <c r="O41" s="86"/>
-      <c r="P41" s="87"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="61"/>
+      <c r="M41" s="62"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="59"/>
       <c r="Q41" s="46"/>
-      <c r="R41" s="72"/>
-      <c r="S41" s="72"/>
+      <c r="R41" s="68"/>
+      <c r="S41" s="68"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="46"/>
       <c r="B42" s="46"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="58"/>
-      <c r="N42" s="85"/>
-      <c r="O42" s="86"/>
-      <c r="P42" s="87"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="62"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="59"/>
       <c r="Q42" s="46"/>
-      <c r="R42" s="72"/>
-      <c r="S42" s="72"/>
+      <c r="R42" s="68"/>
+      <c r="S42" s="68"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="46"/>
       <c r="B43" s="46"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="58"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="86"/>
-      <c r="P43" s="87"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
+      <c r="L43" s="61"/>
+      <c r="M43" s="62"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="59"/>
       <c r="Q43" s="46"/>
-      <c r="R43" s="72"/>
-      <c r="S43" s="72"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="68"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="58"/>
-      <c r="N44" s="85"/>
-      <c r="O44" s="86"/>
-      <c r="P44" s="87"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="61"/>
+      <c r="J44" s="61"/>
+      <c r="K44" s="61"/>
+      <c r="L44" s="61"/>
+      <c r="M44" s="62"/>
+      <c r="N44" s="57"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="59"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="72"/>
-      <c r="S44" s="72"/>
+      <c r="R44" s="68"/>
+      <c r="S44" s="68"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="46"/>
       <c r="B45" s="46"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="85"/>
-      <c r="O45" s="86"/>
-      <c r="P45" s="87"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="61"/>
+      <c r="L45" s="61"/>
+      <c r="M45" s="62"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="59"/>
       <c r="Q45" s="46"/>
-      <c r="R45" s="72"/>
-      <c r="S45" s="72"/>
+      <c r="R45" s="68"/>
+      <c r="S45" s="68"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="46"/>
       <c r="B46" s="46"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="58"/>
-      <c r="N46" s="85"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="87"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="62"/>
+      <c r="N46" s="57"/>
+      <c r="O46" s="58"/>
+      <c r="P46" s="59"/>
       <c r="Q46" s="46"/>
-      <c r="R46" s="72"/>
-      <c r="S46" s="72"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="68"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="58"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="86"/>
-      <c r="P47" s="87"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="61"/>
+      <c r="M47" s="62"/>
+      <c r="N47" s="57"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="59"/>
       <c r="Q47" s="46"/>
-      <c r="R47" s="72"/>
-      <c r="S47" s="72"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="68"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="72"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="R48" s="68"/>
+      <c r="S48" s="68"/>
     </row>
     <row r="49" spans="3:7" ht="30" customHeight="1">
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
     </row>
     <row r="50" spans="3:7" ht="30" customHeight="1"/>
     <row r="51" spans="3:7" ht="30" customHeight="1"/>
     <row r="52" spans="3:7" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="188">
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="R31:S31"/>
     <mergeCell ref="R36:S36"/>
     <mergeCell ref="R37:S37"/>
     <mergeCell ref="N28:P28"/>
@@ -13805,134 +13862,49 @@
     <mergeCell ref="R46:S46"/>
     <mergeCell ref="R38:S38"/>
     <mergeCell ref="R39:S39"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N41:P41"/>
     <mergeCell ref="H20:M20"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="H13:M13"/>
     <mergeCell ref="H14:M14"/>
-    <mergeCell ref="H12:M12"/>
     <mergeCell ref="H16:M16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
     <mergeCell ref="H23:M23"/>
     <mergeCell ref="H24:M24"/>
     <mergeCell ref="H21:M21"/>
     <mergeCell ref="H22:M22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
